--- a/normalized_outputs/normalized_vacancy_rate_by_tract.xlsx
+++ b/normalized_outputs/normalized_vacancy_rate_by_tract.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E986"/>
+  <dimension ref="A1:F986"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,6 +377,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>vacancy_zscore_raw</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>vacancy_zscore</t>
         </is>
       </c>
@@ -394,6 +399,9 @@
       <c r="E2">
         <v>1.565628013236011</v>
       </c>
+      <c r="F2">
+        <v>1.565628013236011</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -408,6 +416,9 @@
       <c r="E3">
         <v>1.466113515427544</v>
       </c>
+      <c r="F3">
+        <v>1.466113515427544</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -422,6 +433,9 @@
       <c r="E4">
         <v>1.357843957484835</v>
       </c>
+      <c r="F4">
+        <v>1.357843957484835</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -436,6 +450,9 @@
       <c r="E5">
         <v>1.253765097406694</v>
       </c>
+      <c r="F5">
+        <v>1.253765097406694</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -450,6 +467,9 @@
       <c r="E6">
         <v>1.151390005946444</v>
       </c>
+      <c r="F6">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -464,6 +484,9 @@
       <c r="E7">
         <v>0.1691392467986642</v>
       </c>
+      <c r="F7">
+        <v>0.1691392467986642</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -478,6 +501,9 @@
       <c r="E8">
         <v>0.04570388872933776</v>
       </c>
+      <c r="F8">
+        <v>0.04570388872933776</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -492,6 +518,9 @@
       <c r="E9">
         <v>-0.04655187402555423</v>
       </c>
+      <c r="F9">
+        <v>-0.04655187402555423</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -506,6 +535,9 @@
       <c r="E10">
         <v>-0.1491572919013952</v>
       </c>
+      <c r="F10">
+        <v>-0.1491572919013952</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -520,6 +552,9 @@
       <c r="E11">
         <v>-0.2200064969058553</v>
       </c>
+      <c r="F11">
+        <v>-0.2200064969058553</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -534,6 +569,9 @@
       <c r="E12">
         <v>1.48264722910441</v>
       </c>
+      <c r="F12">
+        <v>1.48264722910441</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -548,6 +586,9 @@
       <c r="E13">
         <v>1.394593780951599</v>
       </c>
+      <c r="F13">
+        <v>1.394593780951599</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -562,6 +603,9 @@
       <c r="E14">
         <v>1.298948862817239</v>
       </c>
+      <c r="F14">
+        <v>1.298948862817239</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -576,6 +620,9 @@
       <c r="E15">
         <v>1.205610878178965</v>
       </c>
+      <c r="F15">
+        <v>1.205610878178965</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -590,6 +637,9 @@
       <c r="E16">
         <v>1.113738995424943</v>
       </c>
+      <c r="F16">
+        <v>1.113738995424943</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -604,6 +654,9 @@
       <c r="E17">
         <v>1.327250887181229</v>
       </c>
+      <c r="F17">
+        <v>1.327250887181229</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -618,6 +671,9 @@
       <c r="E18">
         <v>1.303649027200853</v>
       </c>
+      <c r="F18">
+        <v>1.303649027200853</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -632,6 +688,9 @@
       <c r="E19">
         <v>1.268842659969324</v>
       </c>
+      <c r="F19">
+        <v>1.268842659969324</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -646,6 +705,9 @@
       <c r="E20">
         <v>1.229231308751077</v>
       </c>
+      <c r="F20">
+        <v>1.229231308751077</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -660,6 +722,9 @@
       <c r="E21">
         <v>1.151390005946444</v>
       </c>
+      <c r="F21">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -674,6 +739,9 @@
       <c r="E22">
         <v>1.297093810715857</v>
       </c>
+      <c r="F22">
+        <v>1.297093810715857</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -688,6 +756,9 @@
       <c r="E23">
         <v>1.235648296240444</v>
       </c>
+      <c r="F23">
+        <v>1.235648296240444</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -702,6 +773,9 @@
       <c r="E24">
         <v>1.167140478279897</v>
       </c>
+      <c r="F24">
+        <v>1.167140478279897</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -716,6 +790,9 @@
       <c r="E25">
         <v>1.097093940694605</v>
       </c>
+      <c r="F25">
+        <v>1.097093940694605</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -730,6 +807,9 @@
       <c r="E26">
         <v>1.028058174949668</v>
       </c>
+      <c r="F26">
+        <v>1.028058174949668</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -744,6 +824,9 @@
       <c r="E27">
         <v>0.7489113599506689</v>
       </c>
+      <c r="F27">
+        <v>0.7489113599506689</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -758,6 +841,9 @@
       <c r="E28">
         <v>0.6948573993708633</v>
       </c>
+      <c r="F28">
+        <v>0.6948573993708633</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -772,6 +858,9 @@
       <c r="E29">
         <v>0.6546902754482272</v>
       </c>
+      <c r="F29">
+        <v>0.6546902754482272</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -786,6 +875,9 @@
       <c r="E30">
         <v>0.6061903900036816</v>
       </c>
+      <c r="F30">
+        <v>0.6061903900036816</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -800,6 +892,9 @@
       <c r="E31">
         <v>0.5670291964442382</v>
       </c>
+      <c r="F31">
+        <v>0.5670291964442382</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -814,6 +909,9 @@
       <c r="E32">
         <v>0.997218180261671</v>
       </c>
+      <c r="F32">
+        <v>0.997218180261671</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -828,6 +926,9 @@
       <c r="E33">
         <v>1.052614026451682</v>
       </c>
+      <c r="F33">
+        <v>1.052614026451682</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -842,6 +943,9 @@
       <c r="E34">
         <v>1.062077145721681</v>
       </c>
+      <c r="F34">
+        <v>1.062077145721681</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -856,6 +960,9 @@
       <c r="E35">
         <v>1.038310109408697</v>
       </c>
+      <c r="F35">
+        <v>1.038310109408697</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -870,6 +977,9 @@
       <c r="E36">
         <v>0.9981387176382378</v>
       </c>
+      <c r="F36">
+        <v>0.9981387176382378</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -884,6 +994,9 @@
       <c r="E37">
         <v>0.8278094659030601</v>
       </c>
+      <c r="F37">
+        <v>0.8278094659030601</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -898,6 +1011,9 @@
       <c r="E38">
         <v>0.7340050603438301</v>
       </c>
+      <c r="F38">
+        <v>0.7340050603438301</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -912,6 +1028,9 @@
       <c r="E39">
         <v>0.6519682968133059</v>
       </c>
+      <c r="F39">
+        <v>0.6519682968133059</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -926,6 +1045,9 @@
       <c r="E40">
         <v>0.5650828418816398</v>
       </c>
+      <c r="F40">
+        <v>0.5650828418816398</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -940,6 +1062,9 @@
       <c r="E41">
         <v>0.4927236188052658</v>
       </c>
+      <c r="F41">
+        <v>0.4927236188052658</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -954,6 +1079,9 @@
       <c r="E42">
         <v>1.065460320230205</v>
       </c>
+      <c r="F42">
+        <v>1.065460320230205</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -968,6 +1096,9 @@
       <c r="E43">
         <v>1.007569710120674</v>
       </c>
+      <c r="F43">
+        <v>1.007569710120674</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -982,6 +1113,9 @@
       <c r="E44">
         <v>0.8813561157676738</v>
       </c>
+      <c r="F44">
+        <v>0.8813561157676738</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -996,6 +1130,9 @@
       <c r="E45">
         <v>0.7971934394007194</v>
       </c>
+      <c r="F45">
+        <v>0.7971934394007194</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1010,6 +1147,9 @@
       <c r="E46">
         <v>0.7005779730956334</v>
       </c>
+      <c r="F46">
+        <v>0.7005779730956334</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1024,6 +1164,9 @@
       <c r="E47">
         <v>0.8664467773486264</v>
       </c>
+      <c r="F47">
+        <v>0.8664467773486264</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1038,6 +1181,9 @@
       <c r="E48">
         <v>0.8931173045301605</v>
       </c>
+      <c r="F48">
+        <v>0.8931173045301605</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1052,6 +1198,9 @@
       <c r="E49">
         <v>0.9092527346568464</v>
       </c>
+      <c r="F49">
+        <v>0.9092527346568464</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1066,6 +1215,9 @@
       <c r="E50">
         <v>0.9094055220769192</v>
       </c>
+      <c r="F50">
+        <v>0.9094055220769192</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1080,6 +1232,9 @@
       <c r="E51">
         <v>0.9054001666065621</v>
       </c>
+      <c r="F51">
+        <v>0.9054001666065621</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1094,6 +1249,9 @@
       <c r="E52">
         <v>1.073352815478049</v>
       </c>
+      <c r="F52">
+        <v>1.073352815478049</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1108,6 +1266,9 @@
       <c r="E53">
         <v>1.118738484093349</v>
       </c>
+      <c r="F53">
+        <v>1.118738484093349</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1122,6 +1283,9 @@
       <c r="E54">
         <v>1.146892617880612</v>
       </c>
+      <c r="F54">
+        <v>1.146892617880612</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1136,6 +1300,9 @@
       <c r="E55">
         <v>1.161203391326423</v>
       </c>
+      <c r="F55">
+        <v>1.161203391326423</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1150,6 +1317,9 @@
       <c r="E56">
         <v>1.151390005946444</v>
       </c>
+      <c r="F56">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1164,6 +1334,9 @@
       <c r="E57">
         <v>-0.7338215196524671</v>
       </c>
+      <c r="F57">
+        <v>-0.7338215196524671</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1178,6 +1351,9 @@
       <c r="E58">
         <v>-0.9304290477474273</v>
       </c>
+      <c r="F58">
+        <v>-0.9304290477474273</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1192,6 +1368,9 @@
       <c r="E59">
         <v>-1.050398904072942</v>
       </c>
+      <c r="F59">
+        <v>-1.050398904072942</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1206,6 +1385,9 @@
       <c r="E60">
         <v>-1.18318404437739</v>
       </c>
+      <c r="F60">
+        <v>-1.18318404437739</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1220,6 +1402,9 @@
       <c r="E61">
         <v>-1.257355520313085</v>
       </c>
+      <c r="F61">
+        <v>-1.257355520313085</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1234,6 +1419,9 @@
       <c r="E62">
         <v>-0.1160385504263219</v>
       </c>
+      <c r="F62">
+        <v>-0.1160385504263219</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1248,6 +1436,9 @@
       <c r="E63">
         <v>-0.2342929473892935</v>
       </c>
+      <c r="F63">
+        <v>-0.2342929473892935</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1262,6 +1453,9 @@
       <c r="E64">
         <v>-0.3157906177017796</v>
       </c>
+      <c r="F64">
+        <v>-0.3157906177017796</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1276,6 +1470,9 @@
       <c r="E65">
         <v>-0.407303387643138</v>
       </c>
+      <c r="F65">
+        <v>-0.407303387643138</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1290,6 +1487,9 @@
       <c r="E66">
         <v>-0.4624317352700363</v>
       </c>
+      <c r="F66">
+        <v>-0.4624317352700363</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1304,6 +1504,9 @@
       <c r="E67">
         <v>1.164000534935338</v>
       </c>
+      <c r="F67">
+        <v>1.164000534935338</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1318,6 +1521,9 @@
       <c r="E68">
         <v>1.19033410112484</v>
       </c>
+      <c r="F68">
+        <v>1.19033410112484</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1332,6 +1538,9 @@
       <c r="E69">
         <v>1.204541236363595</v>
       </c>
+      <c r="F69">
+        <v>1.204541236363595</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1346,6 +1555,9 @@
       <c r="E70">
         <v>1.207846877585808</v>
       </c>
+      <c r="F70">
+        <v>1.207846877585808</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1360,6 +1572,9 @@
       <c r="E71">
         <v>1.151390005946444</v>
       </c>
+      <c r="F71">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1374,6 +1589,9 @@
       <c r="E72">
         <v>1.06554713253342</v>
       </c>
+      <c r="F72">
+        <v>1.06554713253342</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1388,6 +1606,9 @@
       <c r="E73">
         <v>1.05846825771425</v>
       </c>
+      <c r="F73">
+        <v>1.05846825771425</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1402,6 +1623,9 @@
       <c r="E74">
         <v>1.044101651716488</v>
       </c>
+      <c r="F74">
+        <v>1.044101651716488</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1416,6 +1640,9 @@
       <c r="E75">
         <v>1.020296020905704</v>
       </c>
+      <c r="F75">
+        <v>1.020296020905704</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1430,6 +1657,9 @@
       <c r="E76">
         <v>0.9935228967973377</v>
       </c>
+      <c r="F76">
+        <v>0.9935228967973377</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1444,6 +1674,9 @@
       <c r="E77">
         <v>1.100932551728743</v>
       </c>
+      <c r="F77">
+        <v>1.100932551728743</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1458,6 +1691,9 @@
       <c r="E78">
         <v>0.9870080068906885</v>
       </c>
+      <c r="F78">
+        <v>0.9870080068906885</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1472,6 +1708,9 @@
       <c r="E79">
         <v>0.8880170817935105</v>
       </c>
+      <c r="F79">
+        <v>0.8880170817935105</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1486,6 +1725,9 @@
       <c r="E80">
         <v>0.7913595794122407</v>
       </c>
+      <c r="F80">
+        <v>0.7913595794122407</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1500,6 +1742,9 @@
       <c r="E81">
         <v>0.7067181082045225</v>
       </c>
+      <c r="F81">
+        <v>0.7067181082045225</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1514,6 +1759,9 @@
       <c r="E82">
         <v>-0.1606233460641858</v>
       </c>
+      <c r="F82">
+        <v>-0.1606233460641858</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1528,6 +1776,9 @@
       <c r="E83">
         <v>-0.2546988239081291</v>
       </c>
+      <c r="F83">
+        <v>-0.2546988239081291</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -1542,6 +1793,9 @@
       <c r="E84">
         <v>-0.2641150999319749</v>
       </c>
+      <c r="F84">
+        <v>-0.2641150999319749</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -1556,6 +1810,9 @@
       <c r="E85">
         <v>-0.2709002224077232</v>
       </c>
+      <c r="F85">
+        <v>-0.2709002224077232</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1570,6 +1827,9 @@
       <c r="E86">
         <v>-0.2421611158522594</v>
       </c>
+      <c r="F86">
+        <v>-0.2421611158522594</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -1584,6 +1844,9 @@
       <c r="E87">
         <v>-0.1600779563867019</v>
       </c>
+      <c r="F87">
+        <v>-0.1600779563867019</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -1598,6 +1861,9 @@
       <c r="E88">
         <v>-0.2011487450834601</v>
       </c>
+      <c r="F88">
+        <v>-0.2011487450834601</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -1612,6 +1878,9 @@
       <c r="E89">
         <v>-0.2432691090267901</v>
       </c>
+      <c r="F89">
+        <v>-0.2432691090267901</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1626,6 +1895,9 @@
       <c r="E90">
         <v>-0.2851913365010506</v>
       </c>
+      <c r="F90">
+        <v>-0.2851913365010506</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -1640,6 +1912,9 @@
       <c r="E91">
         <v>-0.3052682521401776</v>
       </c>
+      <c r="F91">
+        <v>-0.3052682521401776</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -1654,6 +1929,9 @@
       <c r="E92">
         <v>0.6456671159636886</v>
       </c>
+      <c r="F92">
+        <v>0.6456671159636886</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -1668,6 +1946,9 @@
       <c r="E93">
         <v>0.5278654698606111</v>
       </c>
+      <c r="F93">
+        <v>0.5278654698606111</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -1682,6 +1963,9 @@
       <c r="E94">
         <v>0.4311703771297056</v>
       </c>
+      <c r="F94">
+        <v>0.4311703771297056</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -1696,6 +1980,9 @@
       <c r="E95">
         <v>0.3301752244774613</v>
       </c>
+      <c r="F95">
+        <v>0.3301752244774613</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -1710,6 +1997,9 @@
       <c r="E96">
         <v>0.250761985226909</v>
       </c>
+      <c r="F96">
+        <v>0.250761985226909</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -1724,6 +2014,9 @@
       <c r="E97">
         <v>-0.4228693286729008</v>
       </c>
+      <c r="F97">
+        <v>-0.4228693286729008</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -1738,6 +2031,9 @@
       <c r="E98">
         <v>-0.4616843788185801</v>
       </c>
+      <c r="F98">
+        <v>-0.4616843788185801</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -1752,6 +2048,9 @@
       <c r="E99">
         <v>-0.4678358212166374</v>
       </c>
+      <c r="F99">
+        <v>-0.4678358212166374</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -1766,6 +2065,9 @@
       <c r="E100">
         <v>-0.4860453584840894</v>
       </c>
+      <c r="F100">
+        <v>-0.4860453584840894</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -1780,6 +2082,9 @@
       <c r="E101">
         <v>-0.4807898247252073</v>
       </c>
+      <c r="F101">
+        <v>-0.4807898247252073</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -1794,6 +2099,9 @@
       <c r="E102">
         <v>-0.156446523592368</v>
       </c>
+      <c r="F102">
+        <v>-0.156446523592368</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -1808,6 +2116,9 @@
       <c r="E103">
         <v>-0.6205044737581045</v>
       </c>
+      <c r="F103">
+        <v>-0.6205044737581045</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -1822,6 +2133,9 @@
       <c r="E104">
         <v>0.02600069515576722</v>
       </c>
+      <c r="F104">
+        <v>0.02600069515576722</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -1836,6 +2150,9 @@
       <c r="E105">
         <v>-0.320986369432999</v>
       </c>
+      <c r="F105">
+        <v>-0.320986369432999</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -1850,6 +2167,9 @@
       <c r="E106">
         <v>0.1809667125669314</v>
       </c>
+      <c r="F106">
+        <v>0.1809667125669314</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -1864,6 +2184,9 @@
       <c r="E107">
         <v>-2.490579943905182</v>
       </c>
+      <c r="F107">
+        <v>-2.490579943905182</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -1878,6 +2201,9 @@
       <c r="E108">
         <v>-2.907889972962385</v>
       </c>
+      <c r="F108">
+        <v>-2.907889972962385</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -1892,6 +2218,9 @@
       <c r="E109">
         <v>-3.20569837029953</v>
       </c>
+      <c r="F109">
+        <v>-3.20569837029953</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -1906,6 +2235,9 @@
       <c r="E110">
         <v>-3.485849439241369</v>
       </c>
+      <c r="F110">
+        <v>-3.485849439241369</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -1920,6 +2252,9 @@
       <c r="E111">
         <v>-3.656074730464853</v>
       </c>
+      <c r="F111">
+        <v>-3.656074730464853</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -1934,6 +2269,9 @@
       <c r="E112">
         <v>1.275265087034543</v>
       </c>
+      <c r="F112">
+        <v>1.275265087034543</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -1948,6 +2286,9 @@
       <c r="E113">
         <v>1.207945685854866</v>
       </c>
+      <c r="F113">
+        <v>1.207945685854866</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -1962,6 +2303,9 @@
       <c r="E114">
         <v>1.132658637299363</v>
       </c>
+      <c r="F114">
+        <v>1.132658637299363</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -1976,6 +2320,9 @@
       <c r="E115">
         <v>1.054849327049257</v>
       </c>
+      <c r="F115">
+        <v>1.054849327049257</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -1990,6 +2337,9 @@
       <c r="E116">
         <v>0.9795868399813525</v>
       </c>
+      <c r="F116">
+        <v>0.9795868399813525</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -2004,6 +2354,9 @@
       <c r="E117">
         <v>0.9959909576411892</v>
       </c>
+      <c r="F117">
+        <v>0.9959909576411892</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -2018,6 +2371,9 @@
       <c r="E118">
         <v>1.126922219883993</v>
       </c>
+      <c r="F118">
+        <v>1.126922219883993</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -2032,6 +2388,9 @@
       <c r="E119">
         <v>1.202952078889435</v>
       </c>
+      <c r="F119">
+        <v>1.202952078889435</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -2046,6 +2405,9 @@
       <c r="E120">
         <v>1.248328956101362</v>
       </c>
+      <c r="F120">
+        <v>1.248328956101362</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -2060,6 +2422,9 @@
       <c r="E121">
         <v>1.151390005946444</v>
       </c>
+      <c r="F121">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -2074,6 +2439,9 @@
       <c r="E122">
         <v>1.011671220797982</v>
       </c>
+      <c r="F122">
+        <v>1.011671220797982</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -2088,6 +2456,9 @@
       <c r="E123">
         <v>0.9460938695807029</v>
       </c>
+      <c r="F123">
+        <v>0.9460938695807029</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -2102,6 +2473,9 @@
       <c r="E124">
         <v>0.8861789906545009</v>
       </c>
+      <c r="F124">
+        <v>0.8861789906545009</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -2116,6 +2490,9 @@
       <c r="E125">
         <v>0.8209893805857008</v>
       </c>
+      <c r="F125">
+        <v>0.8209893805857008</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -2130,6 +2507,9 @@
       <c r="E126">
         <v>0.7624281702288932</v>
       </c>
+      <c r="F126">
+        <v>0.7624281702288932</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -2144,6 +2524,9 @@
       <c r="E127">
         <v>0.5652725514653836</v>
       </c>
+      <c r="F127">
+        <v>0.5652725514653836</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -2158,6 +2541,9 @@
       <c r="E128">
         <v>0.4755307631691989</v>
       </c>
+      <c r="F128">
+        <v>0.4755307631691989</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -2172,6 +2558,9 @@
       <c r="E129">
         <v>0.4119534132150852</v>
       </c>
+      <c r="F129">
+        <v>0.4119534132150852</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -2186,6 +2575,9 @@
       <c r="E130">
         <v>0.3418643640074063</v>
       </c>
+      <c r="F130">
+        <v>0.3418643640074063</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -2200,6 +2592,9 @@
       <c r="E131">
         <v>0.2899391869906364</v>
       </c>
+      <c r="F131">
+        <v>0.2899391869906364</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -2214,6 +2609,9 @@
       <c r="E132">
         <v>0.4274913341367049</v>
       </c>
+      <c r="F132">
+        <v>0.4274913341367049</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -2228,6 +2626,9 @@
       <c r="E133">
         <v>0.3694838045388004</v>
       </c>
+      <c r="F133">
+        <v>0.3694838045388004</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -2242,6 +2643,9 @@
       <c r="E134">
         <v>0.3386595361967994</v>
       </c>
+      <c r="F134">
+        <v>0.3386595361967994</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -2256,6 +2660,9 @@
       <c r="E135">
         <v>0.2966786465555733</v>
       </c>
+      <c r="F135">
+        <v>0.2966786465555733</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -2270,6 +2677,9 @@
       <c r="E136">
         <v>0.2701964711642792</v>
       </c>
+      <c r="F136">
+        <v>0.2701964711642792</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -2284,6 +2694,9 @@
       <c r="E137">
         <v>0.2276763347415172</v>
       </c>
+      <c r="F137">
+        <v>0.2276763347415172</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -2298,6 +2711,9 @@
       <c r="E138">
         <v>-0.009902877719811624</v>
       </c>
+      <c r="F138">
+        <v>-0.009902877719811624</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -2312,6 +2728,9 @@
       <c r="E139">
         <v>-0.1358404068040972</v>
       </c>
+      <c r="F139">
+        <v>-0.1358404068040972</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -2326,6 +2745,9 @@
       <c r="E140">
         <v>-0.2299328112155727</v>
       </c>
+      <c r="F140">
+        <v>-0.2299328112155727</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -2340,6 +2762,9 @@
       <c r="E141">
         <v>-0.2686761467194644</v>
       </c>
+      <c r="F141">
+        <v>-0.2686761467194644</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -2354,6 +2779,9 @@
       <c r="E142">
         <v>0.5777980059500056</v>
       </c>
+      <c r="F142">
+        <v>0.5777980059500056</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -2368,6 +2796,9 @@
       <c r="E143">
         <v>0.5091103779364949</v>
       </c>
+      <c r="F143">
+        <v>0.5091103779364949</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -2382,6 +2813,9 @@
       <c r="E144">
         <v>0.4684059861172015</v>
       </c>
+      <c r="F144">
+        <v>0.4684059861172015</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -2396,6 +2830,9 @@
       <c r="E145">
         <v>0.4196688610391743</v>
       </c>
+      <c r="F145">
+        <v>0.4196688610391743</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -2410,6 +2847,9 @@
       <c r="E146">
         <v>0.3847860708915212</v>
       </c>
+      <c r="F146">
+        <v>0.3847860708915212</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -2424,6 +2864,9 @@
       <c r="E147">
         <v>1.094317817029264</v>
       </c>
+      <c r="F147">
+        <v>1.094317817029264</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -2438,6 +2881,9 @@
       <c r="E148">
         <v>1.054535398578073</v>
       </c>
+      <c r="F148">
+        <v>1.054535398578073</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -2452,6 +2898,9 @@
       <c r="E149">
         <v>0.9580866433609309</v>
       </c>
+      <c r="F149">
+        <v>0.9580866433609309</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -2466,6 +2915,9 @@
       <c r="E150">
         <v>0.8862760983462609</v>
       </c>
+      <c r="F150">
+        <v>0.8862760983462609</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -2480,6 +2932,9 @@
       <c r="E151">
         <v>0.8093857546907294</v>
       </c>
+      <c r="F151">
+        <v>0.8093857546907294</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -2494,6 +2949,9 @@
       <c r="E152">
         <v>-0.03783743734075914</v>
       </c>
+      <c r="F152">
+        <v>-0.03783743734075914</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -2508,6 +2966,9 @@
       <c r="E153">
         <v>0.0499178905162671</v>
       </c>
+      <c r="F153">
+        <v>0.0499178905162671</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -2522,6 +2983,9 @@
       <c r="E154">
         <v>0.05925824773021984</v>
       </c>
+      <c r="F154">
+        <v>0.05925824773021984</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -2536,6 +3000,9 @@
       <c r="E155">
         <v>0.0965519232044988</v>
       </c>
+      <c r="F155">
+        <v>0.0965519232044988</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -2550,6 +3017,9 @@
       <c r="E156">
         <v>0.1214385783835484</v>
       </c>
+      <c r="F156">
+        <v>0.1214385783835484</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -2564,6 +3034,9 @@
       <c r="E157">
         <v>-0.3041827317889164</v>
       </c>
+      <c r="F157">
+        <v>-0.3041827317889164</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -2578,6 +3051,9 @@
       <c r="E158">
         <v>-0.4533220318598404</v>
       </c>
+      <c r="F158">
+        <v>-0.4533220318598404</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -2592,6 +3068,9 @@
       <c r="E159">
         <v>-0.3912119329008077</v>
       </c>
+      <c r="F159">
+        <v>-0.3912119329008077</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -2606,6 +3085,9 @@
       <c r="E160">
         <v>-0.455773349742916</v>
       </c>
+      <c r="F160">
+        <v>-0.455773349742916</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -2620,6 +3102,9 @@
       <c r="E161">
         <v>-0.4246382710024157</v>
       </c>
+      <c r="F161">
+        <v>-0.4246382710024157</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -2634,6 +3119,9 @@
       <c r="E162">
         <v>1.200762062099753</v>
       </c>
+      <c r="F162">
+        <v>1.200762062099753</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -2648,6 +3136,9 @@
       <c r="E163">
         <v>1.226037876772013</v>
       </c>
+      <c r="F163">
+        <v>1.226037876772013</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -2662,6 +3153,9 @@
       <c r="E164">
         <v>1.238758875679123</v>
       </c>
+      <c r="F164">
+        <v>1.238758875679123</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -2676,6 +3170,9 @@
       <c r="E165">
         <v>1.240939451975445</v>
       </c>
+      <c r="F165">
+        <v>1.240939451975445</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -2690,6 +3187,9 @@
       <c r="E166">
         <v>1.151390005946444</v>
       </c>
+      <c r="F166">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -2704,6 +3204,9 @@
       <c r="E167">
         <v>0.5502164897323233</v>
       </c>
+      <c r="F167">
+        <v>0.5502164897323233</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -2718,6 +3221,9 @@
       <c r="E168">
         <v>0.5343024631940925</v>
       </c>
+      <c r="F168">
+        <v>0.5343024631940925</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -2732,6 +3238,9 @@
       <c r="E169">
         <v>0.5317342604289214</v>
       </c>
+      <c r="F169">
+        <v>0.5317342604289214</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -2746,6 +3255,9 @@
       <c r="E170">
         <v>0.5150789311001893</v>
       </c>
+      <c r="F170">
+        <v>0.5150789311001893</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -2760,6 +3272,9 @@
       <c r="E171">
         <v>0.5057998513130106</v>
       </c>
+      <c r="F171">
+        <v>0.5057998513130106</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -2774,6 +3289,9 @@
       <c r="E172">
         <v>0.3610248743442097</v>
       </c>
+      <c r="F172">
+        <v>0.3610248743442097</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -2788,6 +3306,9 @@
       <c r="E173">
         <v>0.2457373271668171</v>
       </c>
+      <c r="F173">
+        <v>0.2457373271668171</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -2802,6 +3323,9 @@
       <c r="E174">
         <v>0.2390684741494698</v>
       </c>
+      <c r="F174">
+        <v>0.2390684741494698</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -2816,6 +3340,9 @@
       <c r="E175">
         <v>0.1542520559212337</v>
       </c>
+      <c r="F175">
+        <v>0.1542520559212337</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -2830,6 +3357,9 @@
       <c r="E176">
         <v>0.1422394593080422</v>
       </c>
+      <c r="F176">
+        <v>0.1422394593080422</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -2844,6 +3374,9 @@
       <c r="E177">
         <v>0.3858043941657214</v>
       </c>
+      <c r="F177">
+        <v>0.3858043941657214</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -2858,6 +3391,9 @@
       <c r="E178">
         <v>0.2479314615054227</v>
       </c>
+      <c r="F178">
+        <v>0.2479314615054227</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -2872,6 +3408,9 @@
       <c r="E179">
         <v>0.1441802227810943</v>
       </c>
+      <c r="F179">
+        <v>0.1441802227810943</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -2886,6 +3425,9 @@
       <c r="E180">
         <v>0.03490635220925912</v>
       </c>
+      <c r="F180">
+        <v>0.03490635220925912</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -2900,6 +3442,9 @@
       <c r="E181">
         <v>-0.04530044166995513</v>
       </c>
+      <c r="F181">
+        <v>-0.04530044166995513</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -2914,6 +3459,9 @@
       <c r="E182">
         <v>1.181504106361187</v>
       </c>
+      <c r="F182">
+        <v>1.181504106361187</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -2928,6 +3476,9 @@
       <c r="E183">
         <v>1.12173403571075</v>
       </c>
+      <c r="F183">
+        <v>1.12173403571075</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -2942,6 +3493,9 @@
       <c r="E184">
         <v>1.060165610218954</v>
       </c>
+      <c r="F184">
+        <v>1.060165610218954</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -2956,6 +3510,9 @@
       <c r="E185">
         <v>0.9951860721079293</v>
       </c>
+      <c r="F185">
+        <v>0.9951860721079293</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -2970,6 +3527,9 @@
       <c r="E186">
         <v>0.9328673333182915</v>
       </c>
+      <c r="F186">
+        <v>0.9328673333182915</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -2984,6 +3544,9 @@
       <c r="E187">
         <v>0.3747445380502485</v>
       </c>
+      <c r="F187">
+        <v>0.3747445380502485</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -2998,6 +3561,9 @@
       <c r="E188">
         <v>0.3948275836898887</v>
       </c>
+      <c r="F188">
+        <v>0.3948275836898887</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -3012,6 +3578,9 @@
       <c r="E189">
         <v>0.368342840829222</v>
       </c>
+      <c r="F189">
+        <v>0.368342840829222</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -3026,6 +3595,9 @@
       <c r="E190">
         <v>0.3568068196148499</v>
       </c>
+      <c r="F190">
+        <v>0.3568068196148499</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -3040,6 +3612,9 @@
       <c r="E191">
         <v>0.3431131661812659</v>
       </c>
+      <c r="F191">
+        <v>0.3431131661812659</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -3054,6 +3629,9 @@
       <c r="E192">
         <v>1.263758354631892</v>
       </c>
+      <c r="F192">
+        <v>1.263758354631892</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -3068,6 +3646,9 @@
       <c r="E193">
         <v>1.220134771614032</v>
       </c>
+      <c r="F193">
+        <v>1.220134771614032</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -3082,6 +3663,9 @@
       <c r="E194">
         <v>1.170963708052678</v>
       </c>
+      <c r="F194">
+        <v>1.170963708052678</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -3096,6 +3680,9 @@
       <c r="E195">
         <v>1.117710561026848</v>
       </c>
+      <c r="F195">
+        <v>1.117710561026848</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -3110,6 +3697,9 @@
       <c r="E196">
         <v>1.063043968902391</v>
       </c>
+      <c r="F196">
+        <v>1.063043968902391</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -3124,6 +3714,9 @@
       <c r="E197">
         <v>0.6129211977962702</v>
       </c>
+      <c r="F197">
+        <v>0.6129211977962702</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -3138,6 +3731,9 @@
       <c r="E198">
         <v>0.6618295502287347</v>
       </c>
+      <c r="F198">
+        <v>0.6618295502287347</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -3152,6 +3748,9 @@
       <c r="E199">
         <v>0.458819740017854</v>
       </c>
+      <c r="F199">
+        <v>0.458819740017854</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -3166,6 +3765,9 @@
       <c r="E200">
         <v>0.4382040185523291</v>
       </c>
+      <c r="F200">
+        <v>0.4382040185523291</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -3180,6 +3782,9 @@
       <c r="E201">
         <v>0.3100161141083345</v>
       </c>
+      <c r="F201">
+        <v>0.3100161141083345</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -3194,6 +3799,9 @@
       <c r="E202">
         <v>1.119881441180165</v>
       </c>
+      <c r="F202">
+        <v>1.119881441180165</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -3208,6 +3816,9 @@
       <c r="E203">
         <v>1.150613796170091</v>
       </c>
+      <c r="F203">
+        <v>1.150613796170091</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -3222,6 +3833,9 @@
       <c r="E204">
         <v>1.170208928715455</v>
       </c>
+      <c r="F204">
+        <v>1.170208928715455</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -3236,6 +3850,9 @@
       <c r="E205">
         <v>1.178016232381623</v>
       </c>
+      <c r="F205">
+        <v>1.178016232381623</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -3250,6 +3867,9 @@
       <c r="E206">
         <v>1.151390005946444</v>
       </c>
+      <c r="F206">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -3264,6 +3884,9 @@
       <c r="E207">
         <v>-0.6677343780229972</v>
       </c>
+      <c r="F207">
+        <v>-0.6677343780229972</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -3278,6 +3901,9 @@
       <c r="E208">
         <v>-0.7540549889667114</v>
       </c>
+      <c r="F208">
+        <v>-0.7540549889667114</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -3292,6 +3918,9 @@
       <c r="E209">
         <v>-0.7829526220810724</v>
       </c>
+      <c r="F209">
+        <v>-0.7829526220810724</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -3306,6 +3935,9 @@
       <c r="E210">
         <v>-0.833650726626164</v>
       </c>
+      <c r="F210">
+        <v>-0.833650726626164</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -3320,6 +3952,9 @@
       <c r="E211">
         <v>-0.8434360793020245</v>
       </c>
+      <c r="F211">
+        <v>-0.8434360793020245</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -3334,6 +3969,9 @@
       <c r="E212">
         <v>-0.4045982135173639</v>
       </c>
+      <c r="F212">
+        <v>-0.4045982135173639</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -3348,6 +3986,9 @@
       <c r="E213">
         <v>-0.5279776023523225</v>
       </c>
+      <c r="F213">
+        <v>-0.5279776023523225</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -3362,6 +4003,9 @@
       <c r="E214">
         <v>-0.6456390452022633</v>
       </c>
+      <c r="F214">
+        <v>-0.6456390452022633</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -3376,6 +4020,9 @@
       <c r="E215">
         <v>-0.7570988834571182</v>
       </c>
+      <c r="F215">
+        <v>-0.7570988834571182</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -3390,6 +4037,9 @@
       <c r="E216">
         <v>-0.8268960370083395</v>
       </c>
+      <c r="F216">
+        <v>-0.8268960370083395</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -3404,6 +4054,9 @@
       <c r="E217">
         <v>0.2850615443785764</v>
       </c>
+      <c r="F217">
+        <v>0.2850615443785764</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -3418,6 +4071,9 @@
       <c r="E218">
         <v>-0.2551069581777562</v>
       </c>
+      <c r="F218">
+        <v>-0.2551069581777562</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -3432,6 +4088,9 @@
       <c r="E219">
         <v>-0.1618596312569238</v>
       </c>
+      <c r="F219">
+        <v>-0.1618596312569238</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -3446,6 +4105,9 @@
       <c r="E220">
         <v>-0.05674018646650431</v>
       </c>
+      <c r="F220">
+        <v>-0.05674018646650431</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -3460,6 +4122,9 @@
       <c r="E221">
         <v>-0.4100991737442884</v>
       </c>
+      <c r="F221">
+        <v>-0.4100991737442884</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -3474,6 +4139,9 @@
       <c r="E222">
         <v>0.4457835187549137</v>
       </c>
+      <c r="F222">
+        <v>0.4457835187549137</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -3488,6 +4156,9 @@
       <c r="E223">
         <v>0.5610016934008266</v>
       </c>
+      <c r="F223">
+        <v>0.5610016934008266</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -3502,6 +4173,9 @@
       <c r="E224">
         <v>0.6214314927044304</v>
       </c>
+      <c r="F224">
+        <v>0.6214314927044304</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -3516,6 +4190,9 @@
       <c r="E225">
         <v>0.6931926307298413</v>
       </c>
+      <c r="F225">
+        <v>0.6931926307298413</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -3530,6 +4207,9 @@
       <c r="E226">
         <v>0.7392739027288221</v>
       </c>
+      <c r="F226">
+        <v>0.7392739027288221</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -3544,6 +4224,9 @@
       <c r="E227">
         <v>-0.8227121309884989</v>
       </c>
+      <c r="F227">
+        <v>-0.8227121309884989</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -3558,6 +4241,9 @@
       <c r="E228">
         <v>-0.7922423685229724</v>
       </c>
+      <c r="F228">
+        <v>-0.7922423685229724</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -3572,6 +4258,9 @@
       <c r="E229">
         <v>-0.6871430870783991</v>
       </c>
+      <c r="F229">
+        <v>-0.6871430870783991</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -3586,6 +4275,9 @@
       <c r="E230">
         <v>-0.6075206978971128</v>
       </c>
+      <c r="F230">
+        <v>-0.6075206978971128</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -3600,6 +4292,9 @@
       <c r="E231">
         <v>-0.5033232887287074</v>
       </c>
+      <c r="F231">
+        <v>-0.5033232887287074</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -3614,6 +4309,9 @@
       <c r="E232">
         <v>-0.494491667597693</v>
       </c>
+      <c r="F232">
+        <v>-0.494491667597693</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -3628,6 +4326,9 @@
       <c r="E233">
         <v>-0.606614480769336</v>
       </c>
+      <c r="F233">
+        <v>-0.606614480769336</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -3642,6 +4343,9 @@
       <c r="E234">
         <v>-0.6605144651424457</v>
       </c>
+      <c r="F234">
+        <v>-0.6605144651424457</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -3656,6 +4360,9 @@
       <c r="E235">
         <v>-0.7317731223789615</v>
       </c>
+      <c r="F235">
+        <v>-0.7317731223789615</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -3670,6 +4377,9 @@
       <c r="E236">
         <v>-0.7617309793014169</v>
       </c>
+      <c r="F236">
+        <v>-0.7617309793014169</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -3684,6 +4394,9 @@
       <c r="E237">
         <v>-2.270235537197127</v>
       </c>
+      <c r="F237">
+        <v>-2.270235537197127</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -3698,6 +4411,9 @@
       <c r="E238">
         <v>-2.416443384772849</v>
       </c>
+      <c r="F238">
+        <v>-2.416443384772849</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -3712,6 +4428,9 @@
       <c r="E239">
         <v>-2.472861278586011</v>
       </c>
+      <c r="F239">
+        <v>-2.472861278586011</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -3726,6 +4445,9 @@
       <c r="E240">
         <v>-2.550709797877246</v>
       </c>
+      <c r="F240">
+        <v>-2.550709797877246</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -3740,6 +4462,9 @@
       <c r="E241">
         <v>-2.54956741919302</v>
       </c>
+      <c r="F241">
+        <v>-2.54956741919302</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -3754,6 +4479,9 @@
       <c r="E242">
         <v>-0.5001303305681718</v>
       </c>
+      <c r="F242">
+        <v>-0.5001303305681718</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -3768,6 +4496,9 @@
       <c r="E243">
         <v>-0.4015829086460586</v>
       </c>
+      <c r="F243">
+        <v>-0.4015829086460586</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -3782,6 +4513,9 @@
       <c r="E244">
         <v>-0.3161462863185966</v>
       </c>
+      <c r="F244">
+        <v>-0.3161462863185966</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -3796,6 +4530,9 @@
       <c r="E245">
         <v>-0.2461606945347188</v>
       </c>
+      <c r="F245">
+        <v>-0.2461606945347188</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -3810,6 +4547,9 @@
       <c r="E246">
         <v>-0.1675815498009092</v>
       </c>
+      <c r="F246">
+        <v>-0.1675815498009092</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -3824,6 +4564,9 @@
       <c r="E247">
         <v>-0.2901191618501222</v>
       </c>
+      <c r="F247">
+        <v>-0.2901191618501222</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -3838,6 +4581,9 @@
       <c r="E248">
         <v>-0.3377819763599112</v>
       </c>
+      <c r="F248">
+        <v>-0.3377819763599112</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -3852,6 +4598,9 @@
       <c r="E249">
         <v>-0.4943904734290964</v>
       </c>
+      <c r="F249">
+        <v>-0.4943904734290964</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -3866,6 +4615,9 @@
       <c r="E250">
         <v>-0.5802547990574846</v>
       </c>
+      <c r="F250">
+        <v>-0.5802547990574846</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -3880,6 +4632,9 @@
       <c r="E251">
         <v>-0.662732709210008</v>
       </c>
+      <c r="F251">
+        <v>-0.662732709210008</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -3894,6 +4649,9 @@
       <c r="E252">
         <v>-0.7110966451433106</v>
       </c>
+      <c r="F252">
+        <v>-0.7110966451433106</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -3908,6 +4666,9 @@
       <c r="E253">
         <v>-0.8449138625638881</v>
       </c>
+      <c r="F253">
+        <v>-0.8449138625638881</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -3922,6 +4683,9 @@
       <c r="E254">
         <v>-0.906755842683668</v>
       </c>
+      <c r="F254">
+        <v>-0.906755842683668</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -3936,6 +4700,9 @@
       <c r="E255">
         <v>-0.9863278959444447</v>
       </c>
+      <c r="F255">
+        <v>-0.9863278959444447</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -3950,6 +4717,9 @@
       <c r="E256">
         <v>-1.017928058943491</v>
       </c>
+      <c r="F256">
+        <v>-1.017928058943491</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -3964,6 +4734,9 @@
       <c r="E257">
         <v>1.280666389912523</v>
       </c>
+      <c r="F257">
+        <v>1.280666389912523</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -3978,6 +4751,9 @@
       <c r="E258">
         <v>1.173685208076024</v>
       </c>
+      <c r="F258">
+        <v>1.173685208076024</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -3992,6 +4768,9 @@
       <c r="E259">
         <v>1.06838805738086</v>
       </c>
+      <c r="F259">
+        <v>1.06838805738086</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -4006,6 +4785,9 @@
       <c r="E260">
         <v>0.9646255169235259</v>
       </c>
+      <c r="F260">
+        <v>0.9646255169235259</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -4020,6 +4802,9 @@
       <c r="E261">
         <v>0.8688995951521641</v>
       </c>
+      <c r="F261">
+        <v>0.8688995951521641</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -4034,6 +4819,9 @@
       <c r="E262">
         <v>0.7442549683926809</v>
       </c>
+      <c r="F262">
+        <v>0.7442549683926809</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -4048,6 +4836,9 @@
       <c r="E263">
         <v>0.751602861218995</v>
       </c>
+      <c r="F263">
+        <v>0.751602861218995</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -4062,6 +4853,9 @@
       <c r="E264">
         <v>0.762778141686527</v>
       </c>
+      <c r="F264">
+        <v>0.762778141686527</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -4076,6 +4870,9 @@
       <c r="E265">
         <v>0.7601078163491858</v>
       </c>
+      <c r="F265">
+        <v>0.7601078163491858</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266">
@@ -4090,6 +4887,9 @@
       <c r="E266">
         <v>0.75777912048701</v>
       </c>
+      <c r="F266">
+        <v>0.75777912048701</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -4104,6 +4904,9 @@
       <c r="E267">
         <v>1.333913437949968</v>
       </c>
+      <c r="F267">
+        <v>1.333913437949968</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -4118,6 +4921,9 @@
       <c r="E268">
         <v>1.230224539995118</v>
       </c>
+      <c r="F268">
+        <v>1.230224539995118</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -4132,6 +4938,9 @@
       <c r="E269">
         <v>1.12567088768693</v>
       </c>
+      <c r="F269">
+        <v>1.12567088768693</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -4146,6 +4955,9 @@
       <c r="E270">
         <v>1.023117787224251</v>
       </c>
+      <c r="F270">
+        <v>1.023117787224251</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -4160,6 +4972,9 @@
       <c r="E271">
         <v>0.9271436616650238</v>
       </c>
+      <c r="F271">
+        <v>0.9271436616650238</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -4174,6 +4989,9 @@
       <c r="E272">
         <v>1.178715961925334</v>
       </c>
+      <c r="F272">
+        <v>1.178715961925334</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -4188,6 +5006,9 @@
       <c r="E273">
         <v>1.071180652880557</v>
       </c>
+      <c r="F273">
+        <v>1.071180652880557</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -4202,6 +5023,9 @@
       <c r="E274">
         <v>0.9920835849851469</v>
       </c>
+      <c r="F274">
+        <v>0.9920835849851469</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -4216,6 +5040,9 @@
       <c r="E275">
         <v>0.8990353955180214</v>
       </c>
+      <c r="F275">
+        <v>0.8990353955180214</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -4230,6 +5057,9 @@
       <c r="E276">
         <v>0.8200944619559325</v>
       </c>
+      <c r="F276">
+        <v>0.8200944619559325</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -4244,6 +5074,9 @@
       <c r="E277">
         <v>0.8191578142039539</v>
       </c>
+      <c r="F277">
+        <v>0.8191578142039539</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -4258,6 +5091,9 @@
       <c r="E278">
         <v>0.7135644405646987</v>
       </c>
+      <c r="F278">
+        <v>0.7135644405646987</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -4272,6 +5108,9 @@
       <c r="E279">
         <v>0.6225662956476437</v>
       </c>
+      <c r="F279">
+        <v>0.6225662956476437</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280">
@@ -4286,6 +5125,9 @@
       <c r="E280">
         <v>0.5286143317446393</v>
       </c>
+      <c r="F280">
+        <v>0.5286143317446393</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281">
@@ -4300,6 +5142,9 @@
       <c r="E281">
         <v>0.4508978492127972</v>
       </c>
+      <c r="F281">
+        <v>0.4508978492127972</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282">
@@ -4314,6 +5159,9 @@
       <c r="E282">
         <v>0.8778143392563225</v>
       </c>
+      <c r="F282">
+        <v>0.8778143392563225</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283">
@@ -4328,6 +5176,9 @@
       <c r="E283">
         <v>0.8250341582036164</v>
       </c>
+      <c r="F283">
+        <v>0.8250341582036164</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284">
@@ -4342,6 +5193,9 @@
       <c r="E284">
         <v>0.6977308227769604</v>
       </c>
+      <c r="F284">
+        <v>0.6977308227769604</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285">
@@ -4356,6 +5210,9 @@
       <c r="E285">
         <v>0.6022432891722563</v>
       </c>
+      <c r="F285">
+        <v>0.6022432891722563</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286">
@@ -4370,6 +5227,9 @@
       <c r="E286">
         <v>0.5105434482760774</v>
       </c>
+      <c r="F286">
+        <v>0.5105434482760774</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287">
@@ -4384,6 +5244,9 @@
       <c r="E287">
         <v>-0.2808439737657474</v>
       </c>
+      <c r="F287">
+        <v>-0.2808439737657474</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288">
@@ -4398,6 +5261,9 @@
       <c r="E288">
         <v>-0.1723321978175444</v>
       </c>
+      <c r="F288">
+        <v>-0.1723321978175444</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289">
@@ -4412,6 +5278,9 @@
       <c r="E289">
         <v>-0.6120912736677105</v>
       </c>
+      <c r="F289">
+        <v>-0.6120912736677105</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290">
@@ -4426,6 +5295,9 @@
       <c r="E290">
         <v>-0.4901772950544907</v>
       </c>
+      <c r="F290">
+        <v>-0.4901772950544907</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291">
@@ -4440,6 +5312,9 @@
       <c r="E291">
         <v>-0.8464209351518489</v>
       </c>
+      <c r="F291">
+        <v>-0.8464209351518489</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292">
@@ -4454,6 +5329,9 @@
       <c r="E292">
         <v>0.8260683939839774</v>
       </c>
+      <c r="F292">
+        <v>0.8260683939839774</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293">
@@ -4468,6 +5346,9 @@
       <c r="E293">
         <v>0.8691545277602118</v>
       </c>
+      <c r="F293">
+        <v>0.8691545277602118</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294">
@@ -4482,6 +5363,9 @@
       <c r="E294">
         <v>0.9029467211804096</v>
       </c>
+      <c r="F294">
+        <v>0.9029467211804096</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295">
@@ -4496,6 +5380,9 @@
       <c r="E295">
         <v>0.922918223633355</v>
       </c>
+      <c r="F295">
+        <v>0.922918223633355</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296">
@@ -4510,6 +5397,9 @@
       <c r="E296">
         <v>0.9364668161012349</v>
       </c>
+      <c r="F296">
+        <v>0.9364668161012349</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297">
@@ -4524,6 +5414,9 @@
       <c r="E297">
         <v>0.01908189431463015</v>
       </c>
+      <c r="F297">
+        <v>0.01908189431463015</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298">
@@ -4538,6 +5431,9 @@
       <c r="E298">
         <v>-0.3260036442004229</v>
       </c>
+      <c r="F298">
+        <v>-0.3260036442004229</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299">
@@ -4552,6 +5448,9 @@
       <c r="E299">
         <v>-0.3474148598236536</v>
       </c>
+      <c r="F299">
+        <v>-0.3474148598236536</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300">
@@ -4566,6 +5465,9 @@
       <c r="E300">
         <v>-0.615114625262798</v>
       </c>
+      <c r="F300">
+        <v>-0.615114625262798</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301">
@@ -4580,6 +5482,9 @@
       <c r="E301">
         <v>-0.6186739755012819</v>
       </c>
+      <c r="F301">
+        <v>-0.6186739755012819</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302">
@@ -4594,6 +5499,9 @@
       <c r="E302">
         <v>-1.666822433466935</v>
       </c>
+      <c r="F302">
+        <v>-1.666822433466935</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303">
@@ -4608,6 +5516,9 @@
       <c r="E303">
         <v>-1.487436572106711</v>
       </c>
+      <c r="F303">
+        <v>-1.487436572106711</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304">
@@ -4622,6 +5533,9 @@
       <c r="E304">
         <v>-1.29364319291155</v>
       </c>
+      <c r="F304">
+        <v>-1.29364319291155</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305">
@@ -4636,6 +5550,9 @@
       <c r="E305">
         <v>-1.130996416480314</v>
       </c>
+      <c r="F305">
+        <v>-1.130996416480314</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306">
@@ -4650,6 +5567,9 @@
       <c r="E306">
         <v>-0.954744610240706</v>
       </c>
+      <c r="F306">
+        <v>-0.954744610240706</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307">
@@ -4664,6 +5584,9 @@
       <c r="E307">
         <v>-0.03738694148508046</v>
       </c>
+      <c r="F307">
+        <v>-0.03738694148508046</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308">
@@ -4678,6 +5601,9 @@
       <c r="E308">
         <v>0.003095198806479609</v>
       </c>
+      <c r="F308">
+        <v>0.003095198806479609</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309">
@@ -4692,6 +5618,9 @@
       <c r="E309">
         <v>0.04139934043599505</v>
       </c>
+      <c r="F309">
+        <v>0.04139934043599505</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310">
@@ -4706,6 +5635,9 @@
       <c r="E310">
         <v>0.06329766363154514</v>
       </c>
+      <c r="F310">
+        <v>0.06329766363154514</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311">
@@ -4720,6 +5652,9 @@
       <c r="E311">
         <v>0.09645442758079906</v>
       </c>
+      <c r="F311">
+        <v>0.09645442758079906</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312">
@@ -4734,6 +5669,9 @@
       <c r="E312">
         <v>-1.255548619549003</v>
       </c>
+      <c r="F312">
+        <v>-1.255548619549003</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313">
@@ -4748,6 +5686,9 @@
       <c r="E313">
         <v>-1.211898459494153</v>
       </c>
+      <c r="F313">
+        <v>-1.211898459494153</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314">
@@ -4762,6 +5703,9 @@
       <c r="E314">
         <v>-1.384164116865638</v>
       </c>
+      <c r="F314">
+        <v>-1.384164116865638</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315">
@@ -4776,6 +5720,9 @@
       <c r="E315">
         <v>-1.439896597358306</v>
       </c>
+      <c r="F315">
+        <v>-1.439896597358306</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316">
@@ -4790,6 +5737,9 @@
       <c r="E316">
         <v>-1.496563486845381</v>
       </c>
+      <c r="F316">
+        <v>-1.496563486845381</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317">
@@ -4804,6 +5754,9 @@
       <c r="E317">
         <v>0.3075956301324899</v>
       </c>
+      <c r="F317">
+        <v>0.3075956301324899</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318">
@@ -4818,6 +5771,9 @@
       <c r="E318">
         <v>0.4492413937121245</v>
       </c>
+      <c r="F318">
+        <v>0.4492413937121245</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319">
@@ -4832,6 +5788,9 @@
       <c r="E319">
         <v>0.5804248699806248</v>
       </c>
+      <c r="F319">
+        <v>0.5804248699806248</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320">
@@ -4846,6 +5805,9 @@
       <c r="E320">
         <v>0.6839233334119308</v>
       </c>
+      <c r="F320">
+        <v>0.6839233334119308</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321">
@@ -4860,6 +5822,9 @@
       <c r="E321">
         <v>0.7764719855467282</v>
       </c>
+      <c r="F321">
+        <v>0.7764719855467282</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322">
@@ -4874,6 +5839,9 @@
       <c r="E322">
         <v>0.05962749784300864</v>
       </c>
+      <c r="F322">
+        <v>0.05962749784300864</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323">
@@ -4888,6 +5856,9 @@
       <c r="E323">
         <v>0.04877738876861162</v>
       </c>
+      <c r="F323">
+        <v>0.04877738876861162</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324">
@@ -4902,6 +5873,9 @@
       <c r="E324">
         <v>0.06489611176481631</v>
       </c>
+      <c r="F324">
+        <v>0.06489611176481631</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325">
@@ -4916,6 +5890,9 @@
       <c r="E325">
         <v>0.06128618717883838</v>
       </c>
+      <c r="F325">
+        <v>0.06128618717883838</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326">
@@ -4930,6 +5907,9 @@
       <c r="E326">
         <v>0.0734265940081615</v>
       </c>
+      <c r="F326">
+        <v>0.0734265940081615</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327">
@@ -4944,6 +5924,9 @@
       <c r="E327">
         <v>0.434068475656794</v>
       </c>
+      <c r="F327">
+        <v>0.434068475656794</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328">
@@ -4958,6 +5941,9 @@
       <c r="E328">
         <v>0.6308543821239723</v>
       </c>
+      <c r="F328">
+        <v>0.6308543821239723</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329">
@@ -4972,6 +5958,9 @@
       <c r="E329">
         <v>0.8069523981647747</v>
       </c>
+      <c r="F329">
+        <v>0.8069523981647747</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330">
@@ -4986,6 +5975,9 @@
       <c r="E330">
         <v>0.9519877029245334</v>
       </c>
+      <c r="F330">
+        <v>0.9519877029245334</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331">
@@ -5000,6 +5992,9 @@
       <c r="E331">
         <v>1.07517613674016</v>
       </c>
+      <c r="F331">
+        <v>1.07517613674016</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332">
@@ -5014,6 +6009,9 @@
       <c r="E332">
         <v>-1.370948035963628</v>
       </c>
+      <c r="F332">
+        <v>-1.370948035963628</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333">
@@ -5028,6 +6026,9 @@
       <c r="E333">
         <v>-1.528612241314445</v>
       </c>
+      <c r="F333">
+        <v>-1.528612241314445</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334">
@@ -5042,6 +6043,9 @@
       <c r="E334">
         <v>-1.65919730210278</v>
       </c>
+      <c r="F334">
+        <v>-1.65919730210278</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335">
@@ -5056,6 +6060,9 @@
       <c r="E335">
         <v>-1.767641776239224</v>
       </c>
+      <c r="F335">
+        <v>-1.767641776239224</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336">
@@ -5070,6 +6077,9 @@
       <c r="E336">
         <v>-1.829891385638059</v>
       </c>
+      <c r="F336">
+        <v>-1.829891385638059</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337">
@@ -5084,6 +6094,9 @@
       <c r="E337">
         <v>0.393166314751243</v>
       </c>
+      <c r="F337">
+        <v>0.393166314751243</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338">
@@ -5098,6 +6111,9 @@
       <c r="E338">
         <v>0.4183138820886098</v>
       </c>
+      <c r="F338">
+        <v>0.4183138820886098</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339">
@@ -5112,6 +6128,9 @@
       <c r="E339">
         <v>0.4559526997765316</v>
       </c>
+      <c r="F339">
+        <v>0.4559526997765316</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340">
@@ -5126,6 +6145,9 @@
       <c r="E340">
         <v>0.4743299251307053</v>
       </c>
+      <c r="F340">
+        <v>0.4743299251307053</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341">
@@ -5140,6 +6162,9 @@
       <c r="E341">
         <v>0.4967564649799805</v>
       </c>
+      <c r="F341">
+        <v>0.4967564649799805</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342">
@@ -5154,6 +6179,9 @@
       <c r="E342">
         <v>0.1926943614333665</v>
       </c>
+      <c r="F342">
+        <v>0.1926943614333665</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343">
@@ -5168,6 +6196,9 @@
       <c r="E343">
         <v>0.2146285612176063</v>
       </c>
+      <c r="F343">
+        <v>0.2146285612176063</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344">
@@ -5182,6 +6213,9 @@
       <c r="E344">
         <v>0.2387376397023863</v>
       </c>
+      <c r="F344">
+        <v>0.2387376397023863</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345">
@@ -5196,6 +6230,9 @@
       <c r="E345">
         <v>0.2483543379658947</v>
       </c>
+      <c r="F345">
+        <v>0.2483543379658947</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346">
@@ -5210,6 +6247,9 @@
       <c r="E346">
         <v>0.2666582330032791</v>
       </c>
+      <c r="F346">
+        <v>0.2666582330032791</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347">
@@ -5224,6 +6264,9 @@
       <c r="E347">
         <v>0.8622231197736452</v>
       </c>
+      <c r="F347">
+        <v>0.8622231197736452</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348">
@@ -5238,6 +6281,9 @@
       <c r="E348">
         <v>0.8168624448052989</v>
       </c>
+      <c r="F348">
+        <v>0.8168624448052989</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349">
@@ -5252,6 +6298,9 @@
       <c r="E349">
         <v>0.7781267327796602</v>
       </c>
+      <c r="F349">
+        <v>0.7781267327796602</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350">
@@ -5266,6 +6315,9 @@
       <c r="E350">
         <v>0.7312620452321422</v>
       </c>
+      <c r="F350">
+        <v>0.7312620452321422</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351">
@@ -5280,6 +6332,9 @@
       <c r="E351">
         <v>0.6906694853448033</v>
       </c>
+      <c r="F351">
+        <v>0.6906694853448033</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352">
@@ -5294,6 +6349,9 @@
       <c r="E352">
         <v>0.76083422056747</v>
       </c>
+      <c r="F352">
+        <v>0.76083422056747</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353">
@@ -5308,6 +6366,9 @@
       <c r="E353">
         <v>0.9248184077865794</v>
       </c>
+      <c r="F353">
+        <v>0.9248184077865794</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354">
@@ -5322,6 +6383,9 @@
       <c r="E354">
         <v>0.8475531334978625</v>
       </c>
+      <c r="F354">
+        <v>0.8475531334978625</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355">
@@ -5336,6 +6400,9 @@
       <c r="E355">
         <v>0.9272479538877048</v>
       </c>
+      <c r="F355">
+        <v>0.9272479538877048</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356">
@@ -5350,6 +6417,9 @@
       <c r="E356">
         <v>0.8814608735894511</v>
       </c>
+      <c r="F356">
+        <v>0.8814608735894511</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357">
@@ -5364,6 +6434,9 @@
       <c r="E357">
         <v>1.565628013236011</v>
       </c>
+      <c r="F357">
+        <v>1.565628013236011</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358">
@@ -5378,6 +6451,9 @@
       <c r="E358">
         <v>1.466113515427544</v>
       </c>
+      <c r="F358">
+        <v>1.466113515427544</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359">
@@ -5392,6 +6468,9 @@
       <c r="E359">
         <v>1.357843957484835</v>
       </c>
+      <c r="F359">
+        <v>1.357843957484835</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360">
@@ -5406,6 +6485,9 @@
       <c r="E360">
         <v>1.253765097406694</v>
       </c>
+      <c r="F360">
+        <v>1.253765097406694</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361">
@@ -5420,6 +6502,9 @@
       <c r="E361">
         <v>1.151390005946444</v>
       </c>
+      <c r="F361">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362">
@@ -5434,6 +6519,9 @@
       <c r="E362">
         <v>-0.4563244711869853</v>
       </c>
+      <c r="F362">
+        <v>-0.4563244711869853</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363">
@@ -5448,6 +6536,9 @@
       <c r="E363">
         <v>-0.3827185794731183</v>
       </c>
+      <c r="F363">
+        <v>-0.3827185794731183</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364">
@@ -5462,6 +6553,9 @@
       <c r="E364">
         <v>-0.713523083050206</v>
       </c>
+      <c r="F364">
+        <v>-0.713523083050206</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365">
@@ -5476,6 +6570,9 @@
       <c r="E365">
         <v>-0.6540131884313009</v>
       </c>
+      <c r="F365">
+        <v>-0.6540131884313009</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366">
@@ -5490,6 +6587,9 @@
       <c r="E366">
         <v>-0.8885175489966302</v>
       </c>
+      <c r="F366">
+        <v>-0.8885175489966302</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367">
@@ -5504,6 +6604,9 @@
       <c r="E367">
         <v>1.109484637792237</v>
       </c>
+      <c r="F367">
+        <v>1.109484637792237</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368">
@@ -5518,6 +6621,9 @@
       <c r="E368">
         <v>0.9397382249945677</v>
       </c>
+      <c r="F368">
+        <v>0.9397382249945677</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369">
@@ -5532,6 +6638,9 @@
       <c r="E369">
         <v>1.017737252874995</v>
       </c>
+      <c r="F369">
+        <v>1.017737252874995</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370">
@@ -5546,6 +6655,9 @@
       <c r="E370">
         <v>0.8591661716117468</v>
       </c>
+      <c r="F370">
+        <v>0.8591661716117468</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371">
@@ -5560,6 +6672,9 @@
       <c r="E371">
         <v>0.9157030614831876</v>
       </c>
+      <c r="F371">
+        <v>0.9157030614831876</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372">
@@ -5574,6 +6689,9 @@
       <c r="E372">
         <v>0.4506151395996808</v>
       </c>
+      <c r="F372">
+        <v>0.4506151395996808</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373">
@@ -5588,6 +6706,9 @@
       <c r="E373">
         <v>0.493705660967137</v>
       </c>
+      <c r="F373">
+        <v>0.493705660967137</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374">
@@ -5602,6 +6723,9 @@
       <c r="E374">
         <v>0.5451494802014439</v>
       </c>
+      <c r="F374">
+        <v>0.5451494802014439</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375">
@@ -5616,6 +6740,9 @@
       <c r="E375">
         <v>0.576437400875077</v>
       </c>
+      <c r="F375">
+        <v>0.576437400875077</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376">
@@ -5630,6 +6757,9 @@
       <c r="E376">
         <v>0.6079788730105314</v>
       </c>
+      <c r="F376">
+        <v>0.6079788730105314</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377">
@@ -5644,6 +6774,9 @@
       <c r="E377">
         <v>0.7321159784013966</v>
       </c>
+      <c r="F377">
+        <v>0.7321159784013966</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378">
@@ -5658,6 +6791,9 @@
       <c r="E378">
         <v>0.8011150310208307</v>
       </c>
+      <c r="F378">
+        <v>0.8011150310208307</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379">
@@ -5672,6 +6808,9 @@
       <c r="E379">
         <v>0.871624145076223</v>
       </c>
+      <c r="F379">
+        <v>0.871624145076223</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380">
@@ -5686,6 +6825,9 @@
       <c r="E380">
         <v>0.9205982318262523</v>
       </c>
+      <c r="F380">
+        <v>0.9205982318262523</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381">
@@ -5700,6 +6842,9 @@
       <c r="E381">
         <v>0.960669089916197</v>
       </c>
+      <c r="F381">
+        <v>0.960669089916197</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382">
@@ -5714,6 +6859,9 @@
       <c r="E382">
         <v>-0.4789102138869353</v>
       </c>
+      <c r="F382">
+        <v>-0.4789102138869353</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383">
@@ -5728,6 +6876,9 @@
       <c r="E383">
         <v>-0.5881009429611512</v>
       </c>
+      <c r="F383">
+        <v>-0.5881009429611512</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384">
@@ -5742,6 +6893,9 @@
       <c r="E384">
         <v>-0.606164317899771</v>
       </c>
+      <c r="F384">
+        <v>-0.606164317899771</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385">
@@ -5756,6 +6910,9 @@
       <c r="E385">
         <v>-0.6311390414828261</v>
       </c>
+      <c r="F385">
+        <v>-0.6311390414828261</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386">
@@ -5770,6 +6927,9 @@
       <c r="E386">
         <v>-0.6168157041521047</v>
       </c>
+      <c r="F386">
+        <v>-0.6168157041521047</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387">
@@ -5784,6 +6944,9 @@
       <c r="E387">
         <v>0.7179473120097234</v>
       </c>
+      <c r="F387">
+        <v>0.7179473120097234</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388">
@@ -5798,6 +6961,9 @@
       <c r="E388">
         <v>0.7202712548559951</v>
       </c>
+      <c r="F388">
+        <v>0.7202712548559951</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389">
@@ -5812,6 +6978,9 @@
       <c r="E389">
         <v>0.7444408824013166</v>
       </c>
+      <c r="F389">
+        <v>0.7444408824013166</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390">
@@ -5826,6 +6995,9 @@
       <c r="E390">
         <v>0.7496621365252172</v>
       </c>
+      <c r="F390">
+        <v>0.7496621365252172</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391">
@@ -5840,6 +7012,9 @@
       <c r="E391">
         <v>0.7551586747828202</v>
       </c>
+      <c r="F391">
+        <v>0.7551586747828202</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392">
@@ -5854,6 +7029,9 @@
       <c r="E392">
         <v>0.838998199592015</v>
       </c>
+      <c r="F392">
+        <v>0.838998199592015</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393">
@@ -5868,6 +7046,9 @@
       <c r="E393">
         <v>0.8347692125441418</v>
       </c>
+      <c r="F393">
+        <v>0.8347692125441418</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394">
@@ -5882,6 +7063,9 @@
       <c r="E394">
         <v>0.8326302850563316</v>
       </c>
+      <c r="F394">
+        <v>0.8326302850563316</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395">
@@ -5896,6 +7080,9 @@
       <c r="E395">
         <v>0.8186164801932569</v>
       </c>
+      <c r="F395">
+        <v>0.8186164801932569</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396">
@@ -5910,6 +7097,9 @@
       <c r="E396">
         <v>0.8050014652433288</v>
       </c>
+      <c r="F396">
+        <v>0.8050014652433288</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397">
@@ -5924,6 +7114,9 @@
       <c r="E397">
         <v>1.23714891852174</v>
       </c>
+      <c r="F397">
+        <v>1.23714891852174</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398">
@@ -5938,6 +7131,9 @@
       <c r="E398">
         <v>1.14154433260548</v>
       </c>
+      <c r="F398">
+        <v>1.14154433260548</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399">
@@ -5952,6 +7148,9 @@
       <c r="E399">
         <v>1.047208552419005</v>
       </c>
+      <c r="F399">
+        <v>1.047208552419005</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400">
@@ -5966,6 +7165,9 @@
       <c r="E400">
         <v>0.9530952152943544</v>
       </c>
+      <c r="F400">
+        <v>0.9530952152943544</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401">
@@ -5980,6 +7182,9 @@
       <c r="E401">
         <v>0.8660834349611347</v>
       </c>
+      <c r="F401">
+        <v>0.8660834349611347</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402">
@@ -5994,6 +7199,9 @@
       <c r="E402">
         <v>0.5259452644180189</v>
       </c>
+      <c r="F402">
+        <v>0.5259452644180189</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403">
@@ -6008,6 +7216,9 @@
       <c r="E403">
         <v>0.422099427692893</v>
       </c>
+      <c r="F403">
+        <v>0.422099427692893</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404">
@@ -6022,6 +7233,9 @@
       <c r="E404">
         <v>0.3408924140385982</v>
       </c>
+      <c r="F404">
+        <v>0.3408924140385982</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405">
@@ -6036,6 +7250,9 @@
       <c r="E405">
         <v>0.2532925326486861</v>
       </c>
+      <c r="F405">
+        <v>0.2532925326486861</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406">
@@ -6050,6 +7267,9 @@
       <c r="E406">
         <v>0.1873300830713018</v>
       </c>
+      <c r="F406">
+        <v>0.1873300830713018</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407">
@@ -6064,6 +7284,9 @@
       <c r="E407">
         <v>0.7466994085465299</v>
       </c>
+      <c r="F407">
+        <v>0.7466994085465299</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408">
@@ -6078,6 +7301,9 @@
       <c r="E408">
         <v>0.8750665909988538</v>
       </c>
+      <c r="F408">
+        <v>0.8750665909988538</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409">
@@ -6092,6 +7318,9 @@
       <c r="E409">
         <v>0.5999210435182118</v>
       </c>
+      <c r="F409">
+        <v>0.5999210435182118</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410">
@@ -6106,6 +7335,9 @@
       <c r="E410">
         <v>0.5680996365106922</v>
       </c>
+      <c r="F410">
+        <v>0.5680996365106922</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411">
@@ -6120,6 +7352,9 @@
       <c r="E411">
         <v>0.6977271068152592</v>
       </c>
+      <c r="F411">
+        <v>0.6977271068152592</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412">
@@ -6134,6 +7369,9 @@
       <c r="E412">
         <v>-0.6801219644508818</v>
       </c>
+      <c r="F412">
+        <v>-0.6801219644508818</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413">
@@ -6148,6 +7386,9 @@
       <c r="E413">
         <v>-0.2425828322773637</v>
       </c>
+      <c r="F413">
+        <v>-0.2425828322773637</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414">
@@ -6162,6 +7403,9 @@
       <c r="E414">
         <v>-0.4422485328961123</v>
       </c>
+      <c r="F414">
+        <v>-0.4422485328961123</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415">
@@ -6176,6 +7420,9 @@
       <c r="E415">
         <v>-0.1953887309452482</v>
       </c>
+      <c r="F415">
+        <v>-0.1953887309452482</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416">
@@ -6190,6 +7437,9 @@
       <c r="E416">
         <v>-0.2660707891355734</v>
       </c>
+      <c r="F416">
+        <v>-0.2660707891355734</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417">
@@ -6204,6 +7454,9 @@
       <c r="E417">
         <v>-1.553747932518331</v>
       </c>
+      <c r="F417">
+        <v>-1.553747932518331</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418">
@@ -6218,6 +7471,9 @@
       <c r="E418">
         <v>-1.410515673532066</v>
       </c>
+      <c r="F418">
+        <v>-1.410515673532066</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419">
@@ -6232,6 +7488,9 @@
       <c r="E419">
         <v>-1.232712512541161</v>
       </c>
+      <c r="F419">
+        <v>-1.232712512541161</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420">
@@ -6246,6 +7505,9 @@
       <c r="E420">
         <v>-1.098634058561289</v>
       </c>
+      <c r="F420">
+        <v>-1.098634058561289</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421">
@@ -6260,6 +7522,9 @@
       <c r="E421">
         <v>-0.9406942493157169</v>
       </c>
+      <c r="F421">
+        <v>-0.9406942493157169</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422">
@@ -6274,6 +7539,9 @@
       <c r="E422">
         <v>0.0512802965462653</v>
       </c>
+      <c r="F422">
+        <v>0.0512802965462653</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423">
@@ -6288,6 +7556,9 @@
       <c r="E423">
         <v>0.183013823846375</v>
       </c>
+      <c r="F423">
+        <v>0.183013823846375</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424">
@@ -6302,6 +7573,9 @@
       <c r="E424">
         <v>0.3255091974133903</v>
       </c>
+      <c r="F424">
+        <v>0.3255091974133903</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425">
@@ -6316,6 +7590,9 @@
       <c r="E425">
         <v>0.4359045594061313</v>
       </c>
+      <c r="F425">
+        <v>0.4359045594061313</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426">
@@ -6330,6 +7607,9 @@
       <c r="E426">
         <v>0.5401121950148295</v>
       </c>
+      <c r="F426">
+        <v>0.5401121950148295</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427">
@@ -6344,6 +7624,9 @@
       <c r="E427">
         <v>-0.5001666794634718</v>
       </c>
+      <c r="F427">
+        <v>-0.5001666794634718</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428">
@@ -6358,6 +7641,9 @@
       <c r="E428">
         <v>-0.4374559831159765</v>
       </c>
+      <c r="F428">
+        <v>-0.4374559831159765</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429">
@@ -6372,6 +7658,9 @@
       <c r="E429">
         <v>-0.4006006322201366</v>
       </c>
+      <c r="F429">
+        <v>-0.4006006322201366</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430">
@@ -6386,6 +7675,9 @@
       <c r="E430">
         <v>-0.3466224408772567</v>
       </c>
+      <c r="F430">
+        <v>-0.3466224408772567</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431">
@@ -6400,6 +7692,9 @@
       <c r="E431">
         <v>-0.3039505343177212</v>
       </c>
+      <c r="F431">
+        <v>-0.3039505343177212</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432">
@@ -6414,6 +7709,9 @@
       <c r="E432">
         <v>-1.64108916502338</v>
       </c>
+      <c r="F432">
+        <v>-1.64108916502338</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433">
@@ -6428,6 +7726,9 @@
       <c r="E433">
         <v>-1.327659644483474</v>
       </c>
+      <c r="F433">
+        <v>-1.327659644483474</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434">
@@ -6442,6 +7743,9 @@
       <c r="E434">
         <v>-1.580954984207509</v>
       </c>
+      <c r="F434">
+        <v>-1.580954984207509</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435">
@@ -6456,6 +7760,9 @@
       <c r="E435">
         <v>-1.397827675546942</v>
       </c>
+      <c r="F435">
+        <v>-1.397827675546942</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436">
@@ -6470,6 +7777,9 @@
       <c r="E436">
         <v>-1.499692110620285</v>
       </c>
+      <c r="F436">
+        <v>-1.499692110620285</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437">
@@ -6484,6 +7794,9 @@
       <c r="E437">
         <v>-1.419868136273582</v>
       </c>
+      <c r="F437">
+        <v>-1.419868136273582</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438">
@@ -6498,6 +7811,9 @@
       <c r="E438">
         <v>-1.700235643705404</v>
       </c>
+      <c r="F438">
+        <v>-1.700235643705404</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439">
@@ -6512,6 +7828,9 @@
       <c r="E439">
         <v>-1.833861285144504</v>
       </c>
+      <c r="F439">
+        <v>-1.833861285144504</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440">
@@ -6526,6 +7845,9 @@
       <c r="E440">
         <v>-1.97233283542587</v>
       </c>
+      <c r="F440">
+        <v>-1.97233283542587</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441">
@@ -6540,6 +7862,9 @@
       <c r="E441">
         <v>-2.030197821011031</v>
       </c>
+      <c r="F441">
+        <v>-2.030197821011031</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442">
@@ -6554,6 +7879,9 @@
       <c r="E442">
         <v>0.718427686294441</v>
       </c>
+      <c r="F442">
+        <v>0.718427686294441</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443">
@@ -6568,6 +7896,9 @@
       <c r="E443">
         <v>0.5891457582222566</v>
       </c>
+      <c r="F443">
+        <v>0.5891457582222566</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444">
@@ -6582,6 +7913,9 @@
       <c r="E444">
         <v>0.515946346883569</v>
       </c>
+      <c r="F444">
+        <v>0.515946346883569</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445">
@@ -6596,6 +7930,9 @@
       <c r="E445">
         <v>0.4581981211360857</v>
       </c>
+      <c r="F445">
+        <v>0.4581981211360857</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446">
@@ -6610,6 +7947,9 @@
       <c r="E446">
         <v>0.4274967934042936</v>
       </c>
+      <c r="F446">
+        <v>0.4274967934042936</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447">
@@ -6624,6 +7964,9 @@
       <c r="E447">
         <v>0.7441345166376353</v>
       </c>
+      <c r="F447">
+        <v>0.7441345166376353</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448">
@@ -6638,6 +7981,9 @@
       <c r="E448">
         <v>0.6607639212864935</v>
       </c>
+      <c r="F448">
+        <v>0.6607639212864935</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449">
@@ -6652,6 +7998,9 @@
       <c r="E449">
         <v>0.6010295656646186</v>
       </c>
+      <c r="F449">
+        <v>0.6010295656646186</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450">
@@ -6666,6 +8015,9 @@
       <c r="E450">
         <v>0.5316386999434054</v>
       </c>
+      <c r="F450">
+        <v>0.5316386999434054</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451">
@@ -6680,6 +8032,9 @@
       <c r="E451">
         <v>0.4763816446636607</v>
       </c>
+      <c r="F451">
+        <v>0.4763816446636607</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452">
@@ -6694,6 +8049,9 @@
       <c r="E452">
         <v>0.731359848133774</v>
       </c>
+      <c r="F452">
+        <v>0.731359848133774</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453">
@@ -6708,6 +8066,9 @@
       <c r="E453">
         <v>0.8965392622626461</v>
       </c>
+      <c r="F453">
+        <v>0.8965392622626461</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454">
@@ -6722,6 +8083,9 @@
       <c r="E454">
         <v>0.6609891096714572</v>
       </c>
+      <c r="F454">
+        <v>0.6609891096714572</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455">
@@ -6736,6 +8100,9 @@
       <c r="E455">
         <v>0.7453565625598226</v>
       </c>
+      <c r="F455">
+        <v>0.7453565625598226</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456">
@@ -6750,6 +8117,9 @@
       <c r="E456">
         <v>0.5801659055753543</v>
       </c>
+      <c r="F456">
+        <v>0.5801659055753543</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457">
@@ -6764,6 +8134,9 @@
       <c r="E457">
         <v>0.4184876833329666</v>
       </c>
+      <c r="F457">
+        <v>0.4184876833329666</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458">
@@ -6778,6 +8151,9 @@
       <c r="E458">
         <v>0.2304765308597525</v>
       </c>
+      <c r="F458">
+        <v>0.2304765308597525</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459">
@@ -6792,6 +8168,9 @@
       <c r="E459">
         <v>0.2707404844124613</v>
       </c>
+      <c r="F459">
+        <v>0.2707404844124613</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460">
@@ -6806,6 +8185,9 @@
       <c r="E460">
         <v>0.1699279016418393</v>
       </c>
+      <c r="F460">
+        <v>0.1699279016418393</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461">
@@ -6820,6 +8202,9 @@
       <c r="E461">
         <v>0.1689380029001636</v>
       </c>
+      <c r="F461">
+        <v>0.1689380029001636</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462">
@@ -6834,6 +8219,9 @@
       <c r="E462">
         <v>1.186113653174021</v>
       </c>
+      <c r="F462">
+        <v>1.186113653174021</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463">
@@ -6848,6 +8236,9 @@
       <c r="E463">
         <v>1.189851296085287</v>
       </c>
+      <c r="F463">
+        <v>1.189851296085287</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464">
@@ -6862,6 +8253,9 @@
       <c r="E464">
         <v>1.178893265470941</v>
       </c>
+      <c r="F464">
+        <v>1.178893265470941</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465">
@@ -6876,6 +8270,9 @@
       <c r="E465">
         <v>1.15784414966441</v>
       </c>
+      <c r="F465">
+        <v>1.15784414966441</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466">
@@ -6890,6 +8287,9 @@
       <c r="E466">
         <v>1.129890619105326</v>
       </c>
+      <c r="F466">
+        <v>1.129890619105326</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467">
@@ -6904,6 +8304,9 @@
       <c r="E467">
         <v>-0.2778449055872726</v>
       </c>
+      <c r="F467">
+        <v>-0.2778449055872726</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468">
@@ -6918,6 +8321,9 @@
       <c r="E468">
         <v>-0.3864821195395842</v>
       </c>
+      <c r="F468">
+        <v>-0.3864821195395842</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469">
@@ -6932,6 +8338,9 @@
       <c r="E469">
         <v>-0.4476570776962492</v>
       </c>
+      <c r="F469">
+        <v>-0.4476570776962492</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470">
@@ -6946,6 +8355,9 @@
       <c r="E470">
         <v>-0.5234421659347087</v>
       </c>
+      <c r="F470">
+        <v>-0.5234421659347087</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471">
@@ -6960,6 +8372,9 @@
       <c r="E471">
         <v>-0.5619764831749723</v>
       </c>
+      <c r="F471">
+        <v>-0.5619764831749723</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472">
@@ -6974,6 +8389,9 @@
       <c r="E472">
         <v>1.076285912411186</v>
       </c>
+      <c r="F472">
+        <v>1.076285912411186</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473">
@@ -6988,6 +8406,9 @@
       <c r="E473">
         <v>1.130083055344077</v>
       </c>
+      <c r="F473">
+        <v>1.130083055344077</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474">
@@ -7002,6 +8423,9 @@
       <c r="E474">
         <v>1.172016213341893</v>
       </c>
+      <c r="F474">
+        <v>1.172016213341893</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475">
@@ -7016,6 +8440,9 @@
       <c r="E475">
         <v>1.199432516769482</v>
       </c>
+      <c r="F475">
+        <v>1.199432516769482</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476">
@@ -7030,6 +8457,9 @@
       <c r="E476">
         <v>1.151390005946444</v>
       </c>
+      <c r="F476">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477">
@@ -7044,6 +8474,9 @@
       <c r="E477">
         <v>-1.437605177010752</v>
       </c>
+      <c r="F477">
+        <v>-1.437605177010752</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478">
@@ -7058,6 +8491,9 @@
       <c r="E478">
         <v>-1.441811123607283</v>
       </c>
+      <c r="F478">
+        <v>-1.441811123607283</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479">
@@ -7072,6 +8508,9 @@
       <c r="E479">
         <v>-1.35276215350785</v>
       </c>
+      <c r="F479">
+        <v>-1.35276215350785</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480">
@@ -7086,6 +8525,9 @@
       <c r="E480">
         <v>-1.307702793300734</v>
       </c>
+      <c r="F480">
+        <v>-1.307702793300734</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481">
@@ -7100,6 +8542,9 @@
       <c r="E481">
         <v>-1.221370909386513</v>
       </c>
+      <c r="F481">
+        <v>-1.221370909386513</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482">
@@ -7114,6 +8559,9 @@
       <c r="E482">
         <v>-0.7130066942345303</v>
       </c>
+      <c r="F482">
+        <v>-0.7130066942345303</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483">
@@ -7128,6 +8576,9 @@
       <c r="E483">
         <v>-0.6260773315979006</v>
       </c>
+      <c r="F483">
+        <v>-0.6260773315979006</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484">
@@ -7142,6 +8593,9 @@
       <c r="E484">
         <v>-0.5122155026294615</v>
       </c>
+      <c r="F484">
+        <v>-0.5122155026294615</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485">
@@ -7156,6 +8610,9 @@
       <c r="E485">
         <v>-0.4407701034340962</v>
       </c>
+      <c r="F485">
+        <v>-0.4407701034340962</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486">
@@ -7170,6 +8627,9 @@
       <c r="E486">
         <v>-0.3554975172214128</v>
       </c>
+      <c r="F486">
+        <v>-0.3554975172214128</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487">
@@ -7184,6 +8644,9 @@
       <c r="E487">
         <v>-0.9672631323232059</v>
       </c>
+      <c r="F487">
+        <v>-0.9672631323232059</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488">
@@ -7198,6 +8661,9 @@
       <c r="E488">
         <v>-0.8092691714343946</v>
       </c>
+      <c r="F488">
+        <v>-0.8092691714343946</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489">
@@ -7212,6 +8678,9 @@
       <c r="E489">
         <v>-0.6122269687946275</v>
       </c>
+      <c r="F489">
+        <v>-0.6122269687946275</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490">
@@ -7226,6 +8695,9 @@
       <c r="E490">
         <v>-0.4608834912861272</v>
       </c>
+      <c r="F490">
+        <v>-0.4608834912861272</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491">
@@ -7240,6 +8712,9 @@
       <c r="E491">
         <v>-0.300924795902504</v>
       </c>
+      <c r="F491">
+        <v>-0.300924795902504</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492">
@@ -7254,6 +8729,9 @@
       <c r="E492">
         <v>-0.03696566793236422</v>
       </c>
+      <c r="F492">
+        <v>-0.03696566793236422</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493">
@@ -7268,6 +8746,9 @@
       <c r="E493">
         <v>0.01776819625201541</v>
       </c>
+      <c r="F493">
+        <v>0.01776819625201541</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494">
@@ -7282,6 +8763,9 @@
       <c r="E494">
         <v>0.09841228926764284</v>
       </c>
+      <c r="F494">
+        <v>0.09841228926764284</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495">
@@ -7296,6 +8780,9 @@
       <c r="E495">
         <v>0.1531204192153818</v>
       </c>
+      <c r="F495">
+        <v>0.1531204192153818</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496">
@@ -7310,6 +8797,9 @@
       <c r="E496">
         <v>0.214788698832829</v>
       </c>
+      <c r="F496">
+        <v>0.214788698832829</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497">
@@ -7324,6 +8814,9 @@
       <c r="E497">
         <v>-1.035652090137804</v>
       </c>
+      <c r="F497">
+        <v>-1.035652090137804</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498">
@@ -7338,6 +8831,9 @@
       <c r="E498">
         <v>-0.9411958239613897</v>
       </c>
+      <c r="F498">
+        <v>-0.9411958239613897</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499">
@@ -7352,6 +8848,9 @@
       <c r="E499">
         <v>-0.7936232003391058</v>
       </c>
+      <c r="F499">
+        <v>-0.7936232003391058</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500">
@@ -7366,6 +8865,9 @@
       <c r="E500">
         <v>-0.6877094047592388</v>
       </c>
+      <c r="F500">
+        <v>-0.6877094047592388</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501">
@@ -7380,6 +8882,9 @@
       <c r="E501">
         <v>-0.5627701681397371</v>
       </c>
+      <c r="F501">
+        <v>-0.5627701681397371</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502">
@@ -7394,6 +8899,9 @@
       <c r="E502">
         <v>0.2207448886633412</v>
       </c>
+      <c r="F502">
+        <v>0.2207448886633412</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503">
@@ -7408,6 +8916,9 @@
       <c r="E503">
         <v>0.2301601521176443</v>
       </c>
+      <c r="F503">
+        <v>0.2301601521176443</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504">
@@ -7422,6 +8933,9 @@
       <c r="E504">
         <v>0.2599231102829704</v>
       </c>
+      <c r="F504">
+        <v>0.2599231102829704</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505">
@@ -7436,6 +8950,9 @@
       <c r="E505">
         <v>0.2698426178162566</v>
       </c>
+      <c r="F505">
+        <v>0.2698426178162566</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506">
@@ -7450,6 +8967,9 @@
       <c r="E506">
         <v>0.2893155324284782</v>
       </c>
+      <c r="F506">
+        <v>0.2893155324284782</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507">
@@ -7464,6 +8984,9 @@
       <c r="E507">
         <v>0.03481031391171088</v>
       </c>
+      <c r="F507">
+        <v>0.03481031391171088</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508">
@@ -7478,6 +9001,9 @@
       <c r="E508">
         <v>0.187339006394042</v>
       </c>
+      <c r="F508">
+        <v>0.187339006394042</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509">
@@ -7492,6 +9018,9 @@
       <c r="E509">
         <v>0.3468304418398143</v>
       </c>
+      <c r="F509">
+        <v>0.3468304418398143</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510">
@@ -7506,6 +9035,9 @@
       <c r="E510">
         <v>0.4723192772799735</v>
       </c>
+      <c r="F510">
+        <v>0.4723192772799735</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511">
@@ -7520,6 +9052,9 @@
       <c r="E511">
         <v>0.5889929380025425</v>
       </c>
+      <c r="F511">
+        <v>0.5889929380025425</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512">
@@ -7534,6 +9069,9 @@
       <c r="E512">
         <v>-1.54756759635572</v>
       </c>
+      <c r="F512">
+        <v>-1.54756759635572</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513">
@@ -7548,6 +9086,9 @@
       <c r="E513">
         <v>-1.593142072858216</v>
       </c>
+      <c r="F513">
+        <v>-1.593142072858216</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514">
@@ -7562,6 +9103,9 @@
       <c r="E514">
         <v>-1.564196849353367</v>
       </c>
+      <c r="F514">
+        <v>-1.564196849353367</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515">
@@ -7576,6 +9120,9 @@
       <c r="E515">
         <v>-1.571959722639851</v>
       </c>
+      <c r="F515">
+        <v>-1.571959722639851</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516">
@@ -7590,6 +9137,9 @@
       <c r="E516">
         <v>-1.528704067952315</v>
       </c>
+      <c r="F516">
+        <v>-1.528704067952315</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517">
@@ -7604,6 +9154,9 @@
       <c r="E517">
         <v>-0.1826922261556234</v>
       </c>
+      <c r="F517">
+        <v>-0.1826922261556234</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518">
@@ -7618,6 +9171,9 @@
       <c r="E518">
         <v>0.4446410373956918</v>
       </c>
+      <c r="F518">
+        <v>0.4446410373956918</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519">
@@ -7632,6 +9188,9 @@
       <c r="E519">
         <v>0.5173571355259583</v>
       </c>
+      <c r="F519">
+        <v>0.5173571355259583</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520">
@@ -7646,6 +9205,9 @@
       <c r="E520">
         <v>1.003670603146657</v>
       </c>
+      <c r="F520">
+        <v>1.003670603146657</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521">
@@ -7660,6 +9222,9 @@
       <c r="E521">
         <v>1.058536527895233</v>
       </c>
+      <c r="F521">
+        <v>1.058536527895233</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522">
@@ -7674,6 +9239,9 @@
       <c r="E522">
         <v>-2.993282961120888</v>
       </c>
+      <c r="F522">
+        <v>-2.993282961120888</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523">
@@ -7688,6 +9256,9 @@
       <c r="E523">
         <v>-3.018223024924458</v>
       </c>
+      <c r="F523">
+        <v>-3.018223024924458</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524">
@@ -7702,6 +9273,9 @@
       <c r="E524">
         <v>-2.913618209404385</v>
       </c>
+      <c r="F524">
+        <v>-2.913618209404385</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525">
@@ -7716,6 +9290,9 @@
       <c r="E525">
         <v>-2.861184011177918</v>
       </c>
+      <c r="F525">
+        <v>-2.861184011177918</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526">
@@ -7730,6 +9307,9 @@
       <c r="E526">
         <v>-2.735602468831724</v>
       </c>
+      <c r="F526">
+        <v>-2.735602468831724</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527">
@@ -7744,6 +9324,9 @@
       <c r="E527">
         <v>-0.08347754797822167</v>
       </c>
+      <c r="F527">
+        <v>-0.08347754797822167</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528">
@@ -7758,6 +9341,9 @@
       <c r="E528">
         <v>0.3016770182883123</v>
       </c>
+      <c r="F528">
+        <v>0.3016770182883123</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529">
@@ -7772,6 +9358,9 @@
       <c r="E529">
         <v>0.6682016425039546</v>
       </c>
+      <c r="F529">
+        <v>0.6682016425039546</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530">
@@ -7786,6 +9375,9 @@
       <c r="E530">
         <v>0.9796825869265574</v>
       </c>
+      <c r="F530">
+        <v>0.9796825869265574</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531">
@@ -7800,6 +9392,9 @@
       <c r="E531">
         <v>1.151390005946444</v>
       </c>
+      <c r="F531">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532">
@@ -7814,6 +9409,9 @@
       <c r="E532">
         <v>-0.236592799616469</v>
       </c>
+      <c r="F532">
+        <v>-0.236592799616469</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533">
@@ -7828,6 +9426,9 @@
       <c r="E533">
         <v>-0.08436703527695562</v>
       </c>
+      <c r="F533">
+        <v>-0.08436703527695562</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534">
@@ -7842,6 +9443,9 @@
       <c r="E534">
         <v>0.1048572878349754</v>
       </c>
+      <c r="F534">
+        <v>0.1048572878349754</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535">
@@ -7856,6 +9460,9 @@
       <c r="E535">
         <v>0.2501653363557456</v>
       </c>
+      <c r="F535">
+        <v>0.2501653363557456</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536">
@@ -7870,6 +9477,9 @@
       <c r="E536">
         <v>0.3902077929344784</v>
       </c>
+      <c r="F536">
+        <v>0.3902077929344784</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537">
@@ -7884,6 +9494,9 @@
       <c r="E537">
         <v>-0.5732283570213573</v>
       </c>
+      <c r="F537">
+        <v>-0.5732283570213573</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538">
@@ -7898,6 +9511,9 @@
       <c r="E538">
         <v>-0.01346739400807389</v>
       </c>
+      <c r="F538">
+        <v>-0.01346739400807389</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539">
@@ -7912,6 +9528,9 @@
       <c r="E539">
         <v>0.4675920284992685</v>
       </c>
+      <c r="F539">
+        <v>0.4675920284992685</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540">
@@ -7926,6 +9545,9 @@
       <c r="E540">
         <v>0.8356189768058967</v>
       </c>
+      <c r="F540">
+        <v>0.8356189768058967</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541">
@@ -7940,6 +9562,9 @@
       <c r="E541">
         <v>1.122957268079289</v>
       </c>
+      <c r="F541">
+        <v>1.122957268079289</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542">
@@ -7954,6 +9579,9 @@
       <c r="E542">
         <v>-0.1518582924508523</v>
       </c>
+      <c r="F542">
+        <v>-0.1518582924508523</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543">
@@ -7968,6 +9596,9 @@
       <c r="E543">
         <v>-0.05870367526565875</v>
       </c>
+      <c r="F543">
+        <v>-0.05870367526565875</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544">
@@ -7982,6 +9613,9 @@
       <c r="E544">
         <v>-0.2238978976649607</v>
       </c>
+      <c r="F544">
+        <v>-0.2238978976649607</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545">
@@ -7996,6 +9630,9 @@
       <c r="E545">
         <v>-0.2471119940944481</v>
       </c>
+      <c r="F545">
+        <v>-0.2471119940944481</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546">
@@ -8010,6 +9647,9 @@
       <c r="E546">
         <v>-0.3175906530396579</v>
       </c>
+      <c r="F546">
+        <v>-0.3175906530396579</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547">
@@ -8024,6 +9664,9 @@
       <c r="E547">
         <v>-2.220047791632882</v>
       </c>
+      <c r="F547">
+        <v>-2.220047791632882</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548">
@@ -8038,6 +9681,9 @@
       <c r="E548">
         <v>-2.177539627894218</v>
       </c>
+      <c r="F548">
+        <v>-2.177539627894218</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549">
@@ -8052,6 +9698,9 @@
       <c r="E549">
         <v>-2.042044867849907</v>
       </c>
+      <c r="F549">
+        <v>-2.042044867849907</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550">
@@ -8066,6 +9715,9 @@
       <c r="E550">
         <v>-1.955978605569071</v>
       </c>
+      <c r="F550">
+        <v>-1.955978605569071</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551">
@@ -8080,6 +9732,9 @@
       <c r="E551">
         <v>-1.820713432812787</v>
       </c>
+      <c r="F551">
+        <v>-1.820713432812787</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552">
@@ -8094,6 +9749,9 @@
       <c r="E552">
         <v>-0.4446303836241308</v>
       </c>
+      <c r="F552">
+        <v>-0.4446303836241308</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553">
@@ -8108,6 +9766,9 @@
       <c r="E553">
         <v>-0.3092647726540035</v>
       </c>
+      <c r="F553">
+        <v>-0.3092647726540035</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554">
@@ -8122,6 +9783,9 @@
       <c r="E554">
         <v>-0.1550255774970763</v>
       </c>
+      <c r="F554">
+        <v>-0.1550255774970763</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555">
@@ -8136,6 +9800,9 @@
       <c r="E555">
         <v>-0.03892541976148833</v>
       </c>
+      <c r="F555">
+        <v>-0.03892541976148833</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556">
@@ -8150,6 +9817,9 @@
       <c r="E556">
         <v>0.08055835925838623</v>
       </c>
+      <c r="F556">
+        <v>0.08055835925838623</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557">
@@ -8164,6 +9834,9 @@
       <c r="E557">
         <v>0.1433914897471678</v>
       </c>
+      <c r="F557">
+        <v>0.1433914897471678</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558">
@@ -8178,6 +9851,9 @@
       <c r="E558">
         <v>0.08696008178893735</v>
       </c>
+      <c r="F558">
+        <v>0.08696008178893735</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559">
@@ -8192,6 +9868,9 @@
       <c r="E559">
         <v>0.05803117141290842</v>
       </c>
+      <c r="F559">
+        <v>0.05803117141290842</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560">
@@ -8206,6 +9885,9 @@
       <c r="E560">
         <v>0.01492027835742557</v>
       </c>
+      <c r="F560">
+        <v>0.01492027835742557</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561">
@@ -8220,6 +9902,9 @@
       <c r="E561">
         <v>-0.006745455501914069</v>
       </c>
+      <c r="F561">
+        <v>-0.006745455501914069</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562">
@@ -8234,6 +9919,9 @@
       <c r="E562">
         <v>-1.125837811663104</v>
       </c>
+      <c r="F562">
+        <v>-1.125837811663104</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563">
@@ -8248,6 +9936,9 @@
       <c r="E563">
         <v>-0.8942032036573184</v>
       </c>
+      <c r="F563">
+        <v>-0.8942032036573184</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564">
@@ -8262,6 +9953,9 @@
       <c r="E564">
         <v>-0.6644740772686284</v>
       </c>
+      <c r="F564">
+        <v>-0.6644740772686284</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565">
@@ -8276,6 +9970,9 @@
       <c r="E565">
         <v>-0.474614574323866</v>
       </c>
+      <c r="F565">
+        <v>-0.474614574323866</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566">
@@ -8290,6 +9987,9 @@
       <c r="E566">
         <v>-0.2831398391271558</v>
       </c>
+      <c r="F566">
+        <v>-0.2831398391271558</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567">
@@ -8304,6 +10004,9 @@
       <c r="E567">
         <v>-1.080727488958873</v>
       </c>
+      <c r="F567">
+        <v>-1.080727488958873</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568">
@@ -8318,6 +10021,9 @@
       <c r="E568">
         <v>-0.9768921703149718</v>
       </c>
+      <c r="F568">
+        <v>-0.9768921703149718</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569">
@@ -8332,6 +10038,9 @@
       <c r="E569">
         <v>-0.8241948826464827</v>
       </c>
+      <c r="F569">
+        <v>-0.8241948826464827</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570">
@@ -8346,6 +10055,9 @@
       <c r="E570">
         <v>-0.7136091477119533</v>
       </c>
+      <c r="F570">
+        <v>-0.7136091477119533</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571">
@@ -8360,6 +10072,9 @@
       <c r="E571">
         <v>-0.5840275211522014</v>
       </c>
+      <c r="F571">
+        <v>-0.5840275211522014</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572">
@@ -8374,6 +10089,9 @@
       <c r="E572">
         <v>-0.3100117858602331</v>
       </c>
+      <c r="F572">
+        <v>-0.3100117858602331</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573">
@@ -8388,6 +10106,9 @@
       <c r="E573">
         <v>-0.05557977069359834</v>
       </c>
+      <c r="F573">
+        <v>-0.05557977069359834</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574">
@@ -8402,6 +10123,9 @@
       <c r="E574">
         <v>0.2100792508587531</v>
       </c>
+      <c r="F574">
+        <v>0.2100792508587531</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575">
@@ -8416,6 +10140,9 @@
       <c r="E575">
         <v>0.4276506684070099</v>
       </c>
+      <c r="F575">
+        <v>0.4276506684070099</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576">
@@ -8430,6 +10157,9 @@
       <c r="E576">
         <v>0.6264761271843344</v>
       </c>
+      <c r="F576">
+        <v>0.6264761271843344</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577">
@@ -8444,6 +10174,9 @@
       <c r="E577">
         <v>-1.069793191421527</v>
       </c>
+      <c r="F577">
+        <v>-1.069793191421527</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578">
@@ -8458,6 +10191,9 @@
       <c r="E578">
         <v>-1.235001301047472</v>
       </c>
+      <c r="F578">
+        <v>-1.235001301047472</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579">
@@ -8472,6 +10208,9 @@
       <c r="E579">
         <v>-1.310677635091928</v>
       </c>
+      <c r="F579">
+        <v>-1.310677635091928</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580">
@@ -8486,6 +10225,9 @@
       <c r="E580">
         <v>-1.403435633527787</v>
       </c>
+      <c r="F580">
+        <v>-1.403435633527787</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581">
@@ -8500,6 +10242,9 @@
       <c r="E581">
         <v>-1.436383744667075</v>
       </c>
+      <c r="F581">
+        <v>-1.436383744667075</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582">
@@ -8514,6 +10259,9 @@
       <c r="E582">
         <v>1.092196980047213</v>
       </c>
+      <c r="F582">
+        <v>1.092196980047213</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583">
@@ -8528,6 +10276,9 @@
       <c r="E583">
         <v>1.277211354164611</v>
       </c>
+      <c r="F583">
+        <v>1.277211354164611</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584">
@@ -8542,6 +10293,9 @@
       <c r="E584">
         <v>1.144968510417626</v>
       </c>
+      <c r="F584">
+        <v>1.144968510417626</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585">
@@ -8556,6 +10310,9 @@
       <c r="E585">
         <v>0.9562086796532228</v>
       </c>
+      <c r="F585">
+        <v>0.9562086796532228</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586">
@@ -8570,6 +10327,9 @@
       <c r="E586">
         <v>1.005931086011498</v>
       </c>
+      <c r="F586">
+        <v>1.005931086011498</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587">
@@ -8584,6 +10344,9 @@
       <c r="E587">
         <v>-1.447697569037828</v>
       </c>
+      <c r="F587">
+        <v>-1.447697569037828</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588">
@@ -8598,6 +10361,9 @@
       <c r="E588">
         <v>-1.425652878138224</v>
       </c>
+      <c r="F588">
+        <v>-1.425652878138224</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589">
@@ -8612,6 +10378,9 @@
       <c r="E589">
         <v>-1.332227235248205</v>
       </c>
+      <c r="F589">
+        <v>-1.332227235248205</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590">
@@ -8626,6 +10395,9 @@
       <c r="E590">
         <v>-1.278022642847532</v>
       </c>
+      <c r="F590">
+        <v>-1.278022642847532</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591">
@@ -8640,6 +10412,9 @@
       <c r="E591">
         <v>-1.185649465639277</v>
       </c>
+      <c r="F591">
+        <v>-1.185649465639277</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592">
@@ -8654,6 +10429,9 @@
       <c r="E592">
         <v>0.1048163157416388</v>
       </c>
+      <c r="F592">
+        <v>0.1048163157416388</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593">
@@ -8668,6 +10446,9 @@
       <c r="E593">
         <v>0.01427355770493861</v>
       </c>
+      <c r="F593">
+        <v>0.01427355770493861</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594">
@@ -8682,6 +10463,9 @@
       <c r="E594">
         <v>-0.04615468067557011</v>
       </c>
+      <c r="F594">
+        <v>-0.04615468067557011</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595">
@@ -8696,6 +10480,9 @@
       <c r="E595">
         <v>-0.1153529068858815</v>
       </c>
+      <c r="F595">
+        <v>-0.1153529068858815</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596">
@@ -8710,6 +10497,9 @@
       <c r="E596">
         <v>-0.158575056294032</v>
       </c>
+      <c r="F596">
+        <v>-0.158575056294032</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597">
@@ -8724,6 +10514,9 @@
       <c r="E597">
         <v>-0.6217493959142508</v>
       </c>
+      <c r="F597">
+        <v>-0.6217493959142508</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598">
@@ -8738,6 +10531,9 @@
       <c r="E598">
         <v>-0.7105669635602065</v>
       </c>
+      <c r="F598">
+        <v>-0.7105669635602065</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599">
@@ -8752,6 +10548,9 @@
       <c r="E599">
         <v>-0.6156699016846244</v>
       </c>
+      <c r="F599">
+        <v>-0.6156699016846244</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600">
@@ -8766,6 +10565,9 @@
       <c r="E600">
         <v>-0.6222552707116148</v>
       </c>
+      <c r="F600">
+        <v>-0.6222552707116148</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601">
@@ -8780,6 +10582,9 @@
       <c r="E601">
         <v>-0.5617700019557901</v>
       </c>
+      <c r="F601">
+        <v>-0.5617700019557901</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602">
@@ -8794,6 +10599,9 @@
       <c r="E602">
         <v>-1.23805412748971</v>
       </c>
+      <c r="F602">
+        <v>-1.23805412748971</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603">
@@ -8808,6 +10616,9 @@
       <c r="E603">
         <v>-1.232941268226757</v>
       </c>
+      <c r="F603">
+        <v>-1.232941268226757</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604">
@@ -8822,6 +10633,9 @@
       <c r="E604">
         <v>-1.16006542147375</v>
       </c>
+      <c r="F604">
+        <v>-1.16006542147375</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605">
@@ -8836,6 +10650,9 @@
       <c r="E605">
         <v>-1.12281566248618</v>
       </c>
+      <c r="F605">
+        <v>-1.12281566248618</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606">
@@ -8850,6 +10667,9 @@
       <c r="E606">
         <v>-1.048756710952051</v>
       </c>
+      <c r="F606">
+        <v>-1.048756710952051</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607">
@@ -8864,6 +10684,9 @@
       <c r="E607">
         <v>-1.152939811172118</v>
       </c>
+      <c r="F607">
+        <v>-1.152939811172118</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608">
@@ -8878,6 +10701,9 @@
       <c r="E608">
         <v>-1.012912149646777</v>
       </c>
+      <c r="F608">
+        <v>-1.012912149646777</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609">
@@ -8892,6 +10718,9 @@
       <c r="E609">
         <v>-0.7856985782422994</v>
       </c>
+      <c r="F609">
+        <v>-0.7856985782422994</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610">
@@ -8906,6 +10735,9 @@
       <c r="E610">
         <v>-0.6210060539025497</v>
       </c>
+      <c r="F610">
+        <v>-0.6210060539025497</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611">
@@ -8920,6 +10752,9 @@
       <c r="E611">
         <v>-0.4422213936088342</v>
       </c>
+      <c r="F611">
+        <v>-0.4422213936088342</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612">
@@ -8934,6 +10769,9 @@
       <c r="E612">
         <v>-1.712690005753758</v>
       </c>
+      <c r="F612">
+        <v>-1.712690005753758</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613">
@@ -8948,6 +10786,9 @@
       <c r="E613">
         <v>-1.556505189252349</v>
       </c>
+      <c r="F613">
+        <v>-1.556505189252349</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614">
@@ -8962,6 +10803,9 @@
       <c r="E614">
         <v>-1.356609345232158</v>
       </c>
+      <c r="F614">
+        <v>-1.356609345232158</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615">
@@ -8976,6 +10820,9 @@
       <c r="E615">
         <v>-1.211088597447762</v>
       </c>
+      <c r="F615">
+        <v>-1.211088597447762</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616">
@@ -8990,6 +10837,9 @@
       <c r="E616">
         <v>-1.04029484990721</v>
       </c>
+      <c r="F616">
+        <v>-1.04029484990721</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617">
@@ -9004,6 +10854,9 @@
       <c r="E617">
         <v>0.3617189818628651</v>
       </c>
+      <c r="F617">
+        <v>0.3617189818628651</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618">
@@ -9018,6 +10871,9 @@
       <c r="E618">
         <v>0.5199346875654971</v>
       </c>
+      <c r="F618">
+        <v>0.5199346875654971</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619">
@@ -9032,6 +10888,9 @@
       <c r="E619">
         <v>0.7021802299306084</v>
       </c>
+      <c r="F619">
+        <v>0.7021802299306084</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620">
@@ -9046,6 +10905,9 @@
       <c r="E620">
         <v>0.8385972504071321</v>
       </c>
+      <c r="F620">
+        <v>0.8385972504071321</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621">
@@ -9060,6 +10922,9 @@
       <c r="E621">
         <v>0.9619671965163723</v>
       </c>
+      <c r="F621">
+        <v>0.9619671965163723</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622">
@@ -9074,6 +10939,9 @@
       <c r="E622">
         <v>-2.079424639771824</v>
       </c>
+      <c r="F622">
+        <v>-2.079424639771824</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623">
@@ -9088,6 +10956,9 @@
       <c r="E623">
         <v>-1.926164963573757</v>
       </c>
+      <c r="F623">
+        <v>-1.926164963573757</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624">
@@ -9102,6 +10973,9 @@
       <c r="E624">
         <v>-1.719737522789192</v>
       </c>
+      <c r="F624">
+        <v>-1.719737522789192</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625">
@@ -9116,6 +10990,9 @@
       <c r="E625">
         <v>-1.563997165543859</v>
       </c>
+      <c r="F625">
+        <v>-1.563997165543859</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626">
@@ -9130,6 +11007,9 @@
       <c r="E626">
         <v>-1.37691042624884</v>
       </c>
+      <c r="F626">
+        <v>-1.37691042624884</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627">
@@ -9144,6 +11024,9 @@
       <c r="E627">
         <v>-0.2126429427028631</v>
       </c>
+      <c r="F627">
+        <v>-0.2126429427028631</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628">
@@ -9158,6 +11041,9 @@
       <c r="E628">
         <v>-0.06317774219997732</v>
       </c>
+      <c r="F628">
+        <v>-0.06317774219997732</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629">
@@ -9172,6 +11058,9 @@
       <c r="E629">
         <v>0.09907956408061817</v>
       </c>
+      <c r="F629">
+        <v>0.09907956408061817</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630">
@@ -9186,6 +11075,9 @@
       <c r="E630">
         <v>0.2245009925190764</v>
       </c>
+      <c r="F630">
+        <v>0.2245009925190764</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631">
@@ -9200,6 +11092,9 @@
       <c r="E631">
         <v>0.3464013599893737</v>
       </c>
+      <c r="F631">
+        <v>0.3464013599893737</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632">
@@ -9214,6 +11109,9 @@
       <c r="E632">
         <v>0.4252325367196231</v>
       </c>
+      <c r="F632">
+        <v>0.4252325367196231</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633">
@@ -9228,6 +11126,9 @@
       <c r="E633">
         <v>0.568645458710708</v>
       </c>
+      <c r="F633">
+        <v>0.568645458710708</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634">
@@ -9242,6 +11143,9 @@
       <c r="E634">
         <v>0.7133979131946018</v>
       </c>
+      <c r="F634">
+        <v>0.7133979131946018</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635">
@@ -9256,6 +11160,9 @@
       <c r="E635">
         <v>0.8293044900572845</v>
       </c>
+      <c r="F635">
+        <v>0.8293044900572845</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636">
@@ -9270,6 +11177,9 @@
       <c r="E636">
         <v>0.9298041176219127</v>
       </c>
+      <c r="F636">
+        <v>0.9298041176219127</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637">
@@ -9284,6 +11194,9 @@
       <c r="E637">
         <v>-1.510763271899564</v>
       </c>
+      <c r="F637">
+        <v>-1.510763271899564</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638">
@@ -9298,6 +11211,9 @@
       <c r="E638">
         <v>-1.59619296428058</v>
       </c>
+      <c r="F638">
+        <v>-1.59619296428058</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639">
@@ -9312,6 +11228,9 @@
       <c r="E639">
         <v>-1.593957599850806</v>
       </c>
+      <c r="F639">
+        <v>-1.593957599850806</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640">
@@ -9326,6 +11245,9 @@
       <c r="E640">
         <v>-1.622544529073877</v>
       </c>
+      <c r="F640">
+        <v>-1.622544529073877</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641">
@@ -9340,6 +11262,9 @@
       <c r="E641">
         <v>-1.595431832943092</v>
       </c>
+      <c r="F641">
+        <v>-1.595431832943092</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642">
@@ -9354,6 +11279,9 @@
       <c r="E642">
         <v>0.3483057853035735</v>
       </c>
+      <c r="F642">
+        <v>0.3483057853035735</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643">
@@ -9368,6 +11296,9 @@
       <c r="E643">
         <v>0.567835543707806</v>
       </c>
+      <c r="F643">
+        <v>0.567835543707806</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644">
@@ -9382,6 +11313,9 @@
       <c r="E644">
         <v>0.4417001162418034</v>
       </c>
+      <c r="F644">
+        <v>0.4417001162418034</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645">
@@ -9396,6 +11330,9 @@
       <c r="E645">
         <v>0.5789362920453439</v>
       </c>
+      <c r="F645">
+        <v>0.5789362920453439</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646">
@@ -9410,6 +11347,9 @@
       <c r="E646">
         <v>0.4991499308715441</v>
       </c>
+      <c r="F646">
+        <v>0.4991499308715441</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647">
@@ -9424,6 +11364,9 @@
       <c r="E647">
         <v>-0.1278411551047773</v>
       </c>
+      <c r="F647">
+        <v>-0.1278411551047773</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648">
@@ -9438,6 +11381,9 @@
       <c r="E648">
         <v>0.01098960667256765</v>
       </c>
+      <c r="F648">
+        <v>0.01098960667256765</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649">
@@ -9452,6 +11398,9 @@
       <c r="E649">
         <v>0.2064819022550314</v>
       </c>
+      <c r="F649">
+        <v>0.2064819022550314</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650">
@@ -9466,6 +11415,9 @@
       <c r="E650">
         <v>0.381507084610564</v>
       </c>
+      <c r="F650">
+        <v>0.381507084610564</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651">
@@ -9480,6 +11432,9 @@
       <c r="E651">
         <v>0.5518225384434899</v>
       </c>
+      <c r="F651">
+        <v>0.5518225384434899</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652">
@@ -9494,6 +11449,9 @@
       <c r="E652">
         <v>-1.015412350041743</v>
       </c>
+      <c r="F652">
+        <v>-1.015412350041743</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653">
@@ -9508,6 +11466,9 @@
       <c r="E653">
         <v>-0.9110883445813384</v>
       </c>
+      <c r="F653">
+        <v>-0.9110883445813384</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654">
@@ -9522,6 +11483,9 @@
       <c r="E654">
         <v>-0.7563427984982299</v>
       </c>
+      <c r="F654">
+        <v>-0.7563427984982299</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655">
@@ -9536,6 +11500,9 @@
       <c r="E655">
         <v>-0.6436944049762207</v>
       </c>
+      <c r="F655">
+        <v>-0.6436944049762207</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656">
@@ -9550,6 +11517,9 @@
       <c r="E656">
         <v>-0.5138073740504452</v>
       </c>
+      <c r="F656">
+        <v>-0.5138073740504452</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657">
@@ -9564,6 +11534,9 @@
       <c r="E657">
         <v>-0.1368021729391573</v>
       </c>
+      <c r="F657">
+        <v>-0.1368021729391573</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658">
@@ -9578,6 +11551,9 @@
       <c r="E658">
         <v>0.1885146161809177</v>
       </c>
+      <c r="F658">
+        <v>0.1885146161809177</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659">
@@ -9592,6 +11568,9 @@
       <c r="E659">
         <v>0.4520684749719047</v>
       </c>
+      <c r="F659">
+        <v>0.4520684749719047</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660">
@@ -9606,6 +11585,9 @@
       <c r="E660">
         <v>0.6464804648111117</v>
       </c>
+      <c r="F660">
+        <v>0.6464804648111117</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661">
@@ -9620,6 +11602,9 @@
       <c r="E661">
         <v>0.8090737138095884</v>
       </c>
+      <c r="F661">
+        <v>0.8090737138095884</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662">
@@ -9634,6 +11619,9 @@
       <c r="E662">
         <v>-0.2022210039613191</v>
       </c>
+      <c r="F662">
+        <v>-0.2022210039613191</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663">
@@ -9648,6 +11636,9 @@
       <c r="E663">
         <v>-0.3099859765648608</v>
       </c>
+      <c r="F663">
+        <v>-0.3099859765648608</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664">
@@ -9662,6 +11653,9 @@
       <c r="E664">
         <v>-0.3220337315304579</v>
       </c>
+      <c r="F664">
+        <v>-0.3220337315304579</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665">
@@ -9676,6 +11670,9 @@
       <c r="E665">
         <v>-0.3730720567432371</v>
       </c>
+      <c r="F665">
+        <v>-0.3730720567432371</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666">
@@ -9690,6 +11687,9 @@
       <c r="E666">
         <v>-0.3852722451133768</v>
       </c>
+      <c r="F666">
+        <v>-0.3852722451133768</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667">
@@ -9704,6 +11704,9 @@
       <c r="E667">
         <v>-0.100886254625482</v>
       </c>
+      <c r="F667">
+        <v>-0.100886254625482</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668">
@@ -9718,6 +11721,9 @@
       <c r="E668">
         <v>-0.0163876524506837</v>
       </c>
+      <c r="F668">
+        <v>-0.0163876524506837</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669">
@@ -9732,6 +11738,9 @@
       <c r="E669">
         <v>0.08968164870243617</v>
       </c>
+      <c r="F669">
+        <v>0.08968164870243617</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670">
@@ -9746,6 +11755,9 @@
       <c r="E670">
         <v>0.1660726765232902</v>
       </c>
+      <c r="F670">
+        <v>0.1660726765232902</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671">
@@ -9760,6 +11772,9 @@
       <c r="E671">
         <v>0.2463082949100861</v>
       </c>
+      <c r="F671">
+        <v>0.2463082949100861</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672">
@@ -9774,6 +11789,9 @@
       <c r="E672">
         <v>-1.744524813257256</v>
       </c>
+      <c r="F672">
+        <v>-1.744524813257256</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673">
@@ -9788,6 +11806,9 @@
       <c r="E673">
         <v>-1.724851475888203</v>
       </c>
+      <c r="F673">
+        <v>-1.724851475888203</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674">
@@ -9802,6 +11823,9 @@
       <c r="E674">
         <v>-1.652103940432944</v>
       </c>
+      <c r="F674">
+        <v>-1.652103940432944</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675">
@@ -9816,6 +11840,9 @@
       <c r="E675">
         <v>-1.624912402016141</v>
       </c>
+      <c r="F675">
+        <v>-1.624912402016141</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676">
@@ -9830,6 +11857,9 @@
       <c r="E676">
         <v>-1.550060748654779</v>
       </c>
+      <c r="F676">
+        <v>-1.550060748654779</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677">
@@ -9844,6 +11874,9 @@
       <c r="E677">
         <v>-1.176814309336537</v>
       </c>
+      <c r="F677">
+        <v>-1.176814309336537</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678">
@@ -9858,6 +11891,9 @@
       <c r="E678">
         <v>-1.130915286798222</v>
       </c>
+      <c r="F678">
+        <v>-1.130915286798222</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679">
@@ -9872,6 +11908,9 @@
       <c r="E679">
         <v>-1.070448395458574</v>
       </c>
+      <c r="F679">
+        <v>-1.070448395458574</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680">
@@ -9886,6 +11925,9 @@
       <c r="E680">
         <v>-1.064335082608304</v>
       </c>
+      <c r="F680">
+        <v>-1.064335082608304</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681">
@@ -9900,6 +11942,9 @@
       <c r="E681">
         <v>-1.028428393211849</v>
       </c>
+      <c r="F681">
+        <v>-1.028428393211849</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682">
@@ -9914,6 +11959,9 @@
       <c r="E682">
         <v>-1.41886673965833</v>
       </c>
+      <c r="F682">
+        <v>-1.41886673965833</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683">
@@ -9928,6 +11976,9 @@
       <c r="E683">
         <v>-0.9601069671284941</v>
       </c>
+      <c r="F683">
+        <v>-0.9601069671284941</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684">
@@ -9942,6 +11993,9 @@
       <c r="E684">
         <v>-0.7966705470336619</v>
       </c>
+      <c r="F684">
+        <v>-0.7966705470336619</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685">
@@ -9956,6 +12010,9 @@
       <c r="E685">
         <v>-0.5244333986490144</v>
       </c>
+      <c r="F685">
+        <v>-0.5244333986490144</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686">
@@ -9970,6 +12027,9 @@
       <c r="E686">
         <v>-0.3298925040883203</v>
       </c>
+      <c r="F686">
+        <v>-0.3298925040883203</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687">
@@ -9984,6 +12044,9 @@
       <c r="E687">
         <v>-1.009091120802532</v>
       </c>
+      <c r="F687">
+        <v>-1.009091120802532</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688">
@@ -9998,6 +12061,9 @@
       <c r="E688">
         <v>-1.116632889874225</v>
       </c>
+      <c r="F688">
+        <v>-1.116632889874225</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689">
@@ -10012,6 +12078,9 @@
       <c r="E689">
         <v>-1.155718456067808</v>
       </c>
+      <c r="F689">
+        <v>-1.155718456067808</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690">
@@ -10026,6 +12095,9 @@
       <c r="E690">
         <v>-1.21871372203978</v>
       </c>
+      <c r="F690">
+        <v>-1.21871372203978</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691">
@@ -10040,6 +12112,9 @@
       <c r="E691">
         <v>-1.230937132488105</v>
       </c>
+      <c r="F691">
+        <v>-1.230937132488105</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692">
@@ -10054,6 +12129,9 @@
       <c r="E692">
         <v>-0.04621669769523217</v>
       </c>
+      <c r="F692">
+        <v>-0.04621669769523217</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693">
@@ -10068,6 +12146,9 @@
       <c r="E693">
         <v>-0.03399791143052474</v>
       </c>
+      <c r="F693">
+        <v>-0.03399791143052474</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694">
@@ -10082,6 +12163,9 @@
       <c r="E694">
         <v>0.009783123308979727</v>
       </c>
+      <c r="F694">
+        <v>0.009783123308979727</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695">
@@ -10096,6 +12180,9 @@
       <c r="E695">
         <v>0.02988546725440869</v>
       </c>
+      <c r="F695">
+        <v>0.02988546725440869</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696">
@@ -10110,6 +12197,9 @@
       <c r="E696">
         <v>0.06360520543990038</v>
       </c>
+      <c r="F696">
+        <v>0.06360520543990038</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697">
@@ -10124,6 +12214,9 @@
       <c r="E697">
         <v>0.3757339795710876</v>
       </c>
+      <c r="F697">
+        <v>0.3757339795710876</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698">
@@ -10138,6 +12231,9 @@
       <c r="E698">
         <v>0.3015307565779172</v>
       </c>
+      <c r="F698">
+        <v>0.3015307565779172</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699">
@@ -10152,6 +12248,9 @@
       <c r="E699">
         <v>0.2508398381377389</v>
       </c>
+      <c r="F699">
+        <v>0.2508398381377389</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700">
@@ -10166,6 +12265,9 @@
       <c r="E700">
         <v>0.1896497100696379</v>
       </c>
+      <c r="F700">
+        <v>0.1896497100696379</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701">
@@ -10180,6 +12282,9 @@
       <c r="E701">
         <v>0.148301487115292</v>
       </c>
+      <c r="F701">
+        <v>0.148301487115292</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702">
@@ -10194,6 +12299,9 @@
       <c r="E702">
         <v>-0.9301086646322365</v>
       </c>
+      <c r="F702">
+        <v>-0.9301086646322365</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703">
@@ -10208,6 +12316,9 @@
       <c r="E703">
         <v>-0.8518263776092738</v>
       </c>
+      <c r="F703">
+        <v>-0.8518263776092738</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704">
@@ -10222,6 +12333,9 @@
       <c r="E704">
         <v>-1.00222475351745</v>
       </c>
+      <c r="F704">
+        <v>-1.00222475351745</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705">
@@ -10236,6 +12350,9 @@
       <c r="E705">
         <v>-0.9155577132801919</v>
       </c>
+      <c r="F705">
+        <v>-0.9155577132801919</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706">
@@ -10250,6 +12367,9 @@
       <c r="E706">
         <v>-1.017475593287124</v>
       </c>
+      <c r="F706">
+        <v>-1.017475593287124</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707">
@@ -10264,6 +12384,9 @@
       <c r="E707">
         <v>-2.211041923051916</v>
       </c>
+      <c r="F707">
+        <v>-2.211041923051916</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708">
@@ -10278,6 +12401,9 @@
       <c r="E708">
         <v>-1.861469957725826</v>
       </c>
+      <c r="F708">
+        <v>-1.861469957725826</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709">
@@ -10292,6 +12418,9 @@
       <c r="E709">
         <v>-2.544545215026315</v>
       </c>
+      <c r="F709">
+        <v>-2.544545215026315</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710">
@@ -10306,6 +12435,9 @@
       <c r="E710">
         <v>-2.185596266419718</v>
       </c>
+      <c r="F710">
+        <v>-2.185596266419718</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711">
@@ -10320,6 +12452,9 @@
       <c r="E711">
         <v>-2.712246748742742</v>
       </c>
+      <c r="F711">
+        <v>-2.712246748742742</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712">
@@ -10334,6 +12469,9 @@
       <c r="E712">
         <v>-1.436008515562157</v>
       </c>
+      <c r="F712">
+        <v>-1.436008515562157</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713">
@@ -10348,6 +12486,9 @@
       <c r="E713">
         <v>-1.380936928651017</v>
       </c>
+      <c r="F713">
+        <v>-1.380936928651017</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714">
@@ -10362,6 +12503,9 @@
       <c r="E714">
         <v>-1.311678473509189</v>
       </c>
+      <c r="F714">
+        <v>-1.311678473509189</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715">
@@ -10376,6 +12520,9 @@
       <c r="E715">
         <v>-1.265888063950414</v>
       </c>
+      <c r="F715">
+        <v>-1.265888063950414</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716">
@@ -10390,6 +12537,9 @@
       <c r="E716">
         <v>-1.184267744143294</v>
       </c>
+      <c r="F716">
+        <v>-1.184267744143294</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717">
@@ -10404,6 +12554,9 @@
       <c r="E717">
         <v>-0.4924401205655998</v>
       </c>
+      <c r="F717">
+        <v>-0.4924401205655998</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718">
@@ -10418,6 +12571,9 @@
       <c r="E718">
         <v>-0.26489112224313</v>
       </c>
+      <c r="F718">
+        <v>-0.26489112224313</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719">
@@ -10432,6 +12588,9 @@
       <c r="E719">
         <v>-0.08370617851678223</v>
       </c>
+      <c r="F719">
+        <v>-0.08370617851678223</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720">
@@ -10446,6 +12605,9 @@
       <c r="E720">
         <v>0.01995559835543738</v>
       </c>
+      <c r="F720">
+        <v>0.01995559835543738</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721">
@@ -10460,6 +12622,9 @@
       <c r="E721">
         <v>0.104352825282821</v>
       </c>
+      <c r="F721">
+        <v>0.104352825282821</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722">
@@ -10474,6 +12639,9 @@
       <c r="E722">
         <v>-0.02937896433883094</v>
       </c>
+      <c r="F722">
+        <v>-0.02937896433883094</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723">
@@ -10488,6 +12656,9 @@
       <c r="E723">
         <v>0.1131768818312161</v>
       </c>
+      <c r="F723">
+        <v>0.1131768818312161</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724">
@@ -10502,6 +12673,9 @@
       <c r="E724">
         <v>0.2370651301003811</v>
       </c>
+      <c r="F724">
+        <v>0.2370651301003811</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725">
@@ -10516,6 +12690,9 @@
       <c r="E725">
         <v>0.3417833885125575</v>
       </c>
+      <c r="F725">
+        <v>0.3417833885125575</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726">
@@ -10530,6 +12707,9 @@
       <c r="E726">
         <v>0.4386081900302712</v>
       </c>
+      <c r="F726">
+        <v>0.4386081900302712</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727">
@@ -10544,6 +12724,9 @@
       <c r="E727">
         <v>-1.072230631459031</v>
       </c>
+      <c r="F727">
+        <v>-1.072230631459031</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728">
@@ -10558,6 +12741,9 @@
       <c r="E728">
         <v>-1.08731834901525</v>
       </c>
+      <c r="F728">
+        <v>-1.08731834901525</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729">
@@ -10572,6 +12758,9 @@
       <c r="E729">
         <v>-0.9921451780990987</v>
       </c>
+      <c r="F729">
+        <v>-0.9921451780990987</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730">
@@ -10586,6 +12775,9 @@
       <c r="E730">
         <v>-0.9490433245165586</v>
       </c>
+      <c r="F730">
+        <v>-0.9490433245165586</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731">
@@ -10600,6 +12792,9 @@
       <c r="E731">
         <v>-0.8687147682379425</v>
       </c>
+      <c r="F731">
+        <v>-0.8687147682379425</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732">
@@ -10614,6 +12809,9 @@
       <c r="E732">
         <v>-0.3831212834838034</v>
       </c>
+      <c r="F732">
+        <v>-0.3831212834838034</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733">
@@ -10628,6 +12826,9 @@
       <c r="E733">
         <v>-0.2893199716440735</v>
       </c>
+      <c r="F733">
+        <v>-0.2893199716440735</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734">
@@ -10642,6 +12843,9 @@
       <c r="E734">
         <v>-0.1431673298093609</v>
       </c>
+      <c r="F734">
+        <v>-0.1431673298093609</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735">
@@ -10656,6 +12860,9 @@
       <c r="E735">
         <v>-0.04443946647114888</v>
       </c>
+      <c r="F735">
+        <v>-0.04443946647114888</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736">
@@ -10670,6 +12877,9 @@
       <c r="E736">
         <v>0.06520874530801631</v>
       </c>
+      <c r="F736">
+        <v>0.06520874530801631</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737">
@@ -10684,6 +12894,9 @@
       <c r="E737">
         <v>-2.126819440207375</v>
       </c>
+      <c r="F737">
+        <v>-2.126819440207375</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738">
@@ -10698,6 +12911,9 @@
       <c r="E738">
         <v>-2.215620260182575</v>
       </c>
+      <c r="F738">
+        <v>-2.215620260182575</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739">
@@ -10712,6 +12928,9 @@
       <c r="E739">
         <v>-2.196865689843064</v>
       </c>
+      <c r="F739">
+        <v>-2.196865689843064</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740">
@@ -10726,6 +12945,9 @@
       <c r="E740">
         <v>-2.215405654380505</v>
       </c>
+      <c r="F740">
+        <v>-2.215405654380505</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741">
@@ -10740,6 +12962,9 @@
       <c r="E741">
         <v>-2.1664526477793</v>
       </c>
+      <c r="F741">
+        <v>-2.1664526477793</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742">
@@ -10754,6 +12979,9 @@
       <c r="E742">
         <v>0.7177092723931323</v>
       </c>
+      <c r="F742">
+        <v>0.7177092723931323</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743">
@@ -10768,6 +12996,9 @@
       <c r="E743">
         <v>0.7189143157724418</v>
       </c>
+      <c r="F743">
+        <v>0.7189143157724418</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744">
@@ -10782,6 +13013,9 @@
       <c r="E744">
         <v>0.7268435627458965</v>
       </c>
+      <c r="F744">
+        <v>0.7268435627458965</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745">
@@ -10796,6 +13030,9 @@
       <c r="E745">
         <v>0.7210516600748713</v>
       </c>
+      <c r="F745">
+        <v>0.7210516600748713</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746">
@@ -10810,6 +13047,9 @@
       <c r="E746">
         <v>0.716815250496984</v>
       </c>
+      <c r="F746">
+        <v>0.716815250496984</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747">
@@ -10824,6 +13064,9 @@
       <c r="E747">
         <v>-0.1781329912994417</v>
       </c>
+      <c r="F747">
+        <v>-0.1781329912994417</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748">
@@ -10838,6 +13081,9 @@
       <c r="E748">
         <v>-0.01546238779433944</v>
       </c>
+      <c r="F748">
+        <v>-0.01546238779433944</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749">
@@ -10852,6 +13098,9 @@
       <c r="E749">
         <v>0.1500683851863668</v>
       </c>
+      <c r="F749">
+        <v>0.1500683851863668</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750">
@@ -10866,6 +13115,9 @@
       <c r="E750">
         <v>0.2808263680336645</v>
       </c>
+      <c r="F750">
+        <v>0.2808263680336645</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751">
@@ -10880,6 +13132,9 @@
       <c r="E751">
         <v>0.4061595041491288</v>
       </c>
+      <c r="F751">
+        <v>0.4061595041491288</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752">
@@ -10894,6 +13149,9 @@
       <c r="E752">
         <v>0.7299564793251639</v>
       </c>
+      <c r="F752">
+        <v>0.7299564793251639</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753">
@@ -10908,6 +13166,9 @@
       <c r="E753">
         <v>0.7636223339258147</v>
       </c>
+      <c r="F753">
+        <v>0.7636223339258147</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754">
@@ -10922,6 +13183,9 @@
       <c r="E754">
         <v>0.8068920550526227</v>
       </c>
+      <c r="F754">
+        <v>0.8068920550526227</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755">
@@ -10936,6 +13200,9 @@
       <c r="E755">
         <v>0.8307043537444492</v>
       </c>
+      <c r="F755">
+        <v>0.8307043537444492</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756">
@@ -10950,6 +13217,9 @@
       <c r="E756">
         <v>0.8506382870639562</v>
       </c>
+      <c r="F756">
+        <v>0.8506382870639562</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757">
@@ -10964,6 +13234,9 @@
       <c r="E757">
         <v>-1.722356231833063</v>
       </c>
+      <c r="F757">
+        <v>-1.722356231833063</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758">
@@ -10978,6 +13251,9 @@
       <c r="E758">
         <v>-1.912350998927283</v>
       </c>
+      <c r="F758">
+        <v>-1.912350998927283</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759">
@@ -10992,6 +13268,9 @@
       <c r="E759">
         <v>-2.002684602808257</v>
       </c>
+      <c r="F759">
+        <v>-2.002684602808257</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760">
@@ -11006,6 +13285,9 @@
       <c r="E760">
         <v>-2.112199206300014</v>
       </c>
+      <c r="F760">
+        <v>-2.112199206300014</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761">
@@ -11020,6 +13302,9 @@
       <c r="E761">
         <v>-2.147895391358772</v>
       </c>
+      <c r="F761">
+        <v>-2.147895391358772</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762">
@@ -11034,6 +13319,9 @@
       <c r="E762">
         <v>1.193454626506777</v>
       </c>
+      <c r="F762">
+        <v>1.193454626506777</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763">
@@ -11048,6 +13336,9 @@
       <c r="E763">
         <v>1.20022918555951</v>
       </c>
+      <c r="F763">
+        <v>1.20022918555951</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764">
@@ -11062,6 +13353,9 @@
       <c r="E764">
         <v>1.188391299876825</v>
       </c>
+      <c r="F764">
+        <v>1.188391299876825</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765">
@@ -11076,6 +13370,9 @@
       <c r="E765">
         <v>1.172046815066639</v>
       </c>
+      <c r="F765">
+        <v>1.172046815066639</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766">
@@ -11090,6 +13387,9 @@
       <c r="E766">
         <v>1.147088268541527</v>
       </c>
+      <c r="F766">
+        <v>1.147088268541527</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767">
@@ -11104,6 +13404,9 @@
       <c r="E767">
         <v>-0.1106089337066853</v>
       </c>
+      <c r="F767">
+        <v>-0.1106089337066853</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768">
@@ -11118,6 +13421,9 @@
       <c r="E768">
         <v>-0.2320748244016466</v>
       </c>
+      <c r="F768">
+        <v>-0.2320748244016466</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769">
@@ -11132,6 +13438,9 @@
       <c r="E769">
         <v>-0.3072081381593459</v>
       </c>
+      <c r="F769">
+        <v>-0.3072081381593459</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770">
@@ -11146,6 +13455,9 @@
       <c r="E770">
         <v>-0.3947309844918651</v>
       </c>
+      <c r="F770">
+        <v>-0.3947309844918651</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771">
@@ -11160,6 +13472,9 @@
       <c r="E771">
         <v>-0.4464061768312509</v>
       </c>
+      <c r="F771">
+        <v>-0.4464061768312509</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772">
@@ -11174,6 +13489,9 @@
       <c r="E772">
         <v>0.7358096624970982</v>
       </c>
+      <c r="F772">
+        <v>0.7358096624970982</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773">
@@ -11188,6 +13506,9 @@
       <c r="E773">
         <v>0.634758794918359</v>
       </c>
+      <c r="F773">
+        <v>0.634758794918359</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774">
@@ -11202,6 +13523,9 @@
       <c r="E774">
         <v>0.5637865680490218</v>
       </c>
+      <c r="F774">
+        <v>0.5637865680490218</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775">
@@ -11216,6 +13540,9 @@
       <c r="E775">
         <v>0.4835458280108175</v>
       </c>
+      <c r="F775">
+        <v>0.4835458280108175</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776">
@@ -11230,6 +13557,9 @@
       <c r="E776">
         <v>0.4198333002411419</v>
       </c>
+      <c r="F776">
+        <v>0.4198333002411419</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777">
@@ -11244,6 +13574,9 @@
       <c r="E777">
         <v>0.9079211034191097</v>
       </c>
+      <c r="F777">
+        <v>0.9079211034191097</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778">
@@ -11258,6 +13591,9 @@
       <c r="E778">
         <v>0.8087814330676436</v>
       </c>
+      <c r="F778">
+        <v>0.8087814330676436</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779">
@@ -11272,6 +13608,9 @@
       <c r="E779">
         <v>0.7042406485703883</v>
       </c>
+      <c r="F779">
+        <v>0.7042406485703883</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780">
@@ -11286,6 +13625,9 @@
       <c r="E780">
         <v>0.586728847918235</v>
       </c>
+      <c r="F780">
+        <v>0.586728847918235</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781">
@@ -11300,6 +13642,9 @@
       <c r="E781">
         <v>0.4794015876151486</v>
       </c>
+      <c r="F781">
+        <v>0.4794015876151486</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782">
@@ -11314,6 +13659,9 @@
       <c r="E782">
         <v>0.7542936871245366</v>
       </c>
+      <c r="F782">
+        <v>0.7542936871245366</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783">
@@ -11328,6 +13676,9 @@
       <c r="E783">
         <v>0.7750493034421478</v>
       </c>
+      <c r="F783">
+        <v>0.7750493034421478</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784">
@@ -11342,6 +13693,9 @@
       <c r="E784">
         <v>0.7981172936146085</v>
       </c>
+      <c r="F784">
+        <v>0.7981172936146085</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785">
@@ -11356,6 +13710,9 @@
       <c r="E785">
         <v>0.8062244448737144</v>
       </c>
+      <c r="F785">
+        <v>0.8062244448737144</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786">
@@ -11370,6 +13727,9 @@
       <c r="E786">
         <v>0.8123398838189311</v>
       </c>
+      <c r="F786">
+        <v>0.8123398838189311</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787">
@@ -11384,6 +13744,9 @@
       <c r="E787">
         <v>-1.116480098664914</v>
       </c>
+      <c r="F787">
+        <v>-1.116480098664914</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788">
@@ -11398,6 +13761,9 @@
       <c r="E788">
         <v>-1.148442802621646</v>
       </c>
+      <c r="F788">
+        <v>-1.148442802621646</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789">
@@ -11412,6 +13778,9 @@
       <c r="E789">
         <v>-1.096847678033576</v>
       </c>
+      <c r="F789">
+        <v>-1.096847678033576</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790">
@@ -11426,6 +13795,9 @@
       <c r="E790">
         <v>-1.074968693191275</v>
       </c>
+      <c r="F790">
+        <v>-1.074968693191275</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791">
@@ -11440,6 +13812,9 @@
       <c r="E791">
         <v>-1.014939719350874</v>
       </c>
+      <c r="F791">
+        <v>-1.014939719350874</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792">
@@ -11454,6 +13829,9 @@
       <c r="E792">
         <v>1.203866573140991</v>
       </c>
+      <c r="F792">
+        <v>1.203866573140991</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793">
@@ -11468,6 +13846,9 @@
       <c r="E793">
         <v>1.407504047160063</v>
       </c>
+      <c r="F793">
+        <v>1.407504047160063</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794">
@@ -11482,6 +13863,9 @@
       <c r="E794">
         <v>1.357843957484835</v>
       </c>
+      <c r="F794">
+        <v>1.357843957484835</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795">
@@ -11496,6 +13880,9 @@
       <c r="E795">
         <v>1.253765097406694</v>
       </c>
+      <c r="F795">
+        <v>1.253765097406694</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796">
@@ -11510,6 +13897,9 @@
       <c r="E796">
         <v>1.151390005946444</v>
       </c>
+      <c r="F796">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797">
@@ -11524,6 +13914,9 @@
       <c r="E797">
         <v>0.856100064362968</v>
       </c>
+      <c r="F797">
+        <v>0.856100064362968</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798">
@@ -11538,6 +13931,9 @@
       <c r="E798">
         <v>0.9462474274793902</v>
       </c>
+      <c r="F798">
+        <v>0.9462474274793902</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799">
@@ -11552,6 +13948,9 @@
       <c r="E799">
         <v>1.025631416048522</v>
       </c>
+      <c r="F799">
+        <v>1.025631416048522</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800">
@@ -11566,6 +13965,9 @@
       <c r="E800">
         <v>1.085369362016983</v>
       </c>
+      <c r="F800">
+        <v>1.085369362016983</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801">
@@ -11580,6 +13982,9 @@
       <c r="E801">
         <v>1.130767333026955</v>
       </c>
+      <c r="F801">
+        <v>1.130767333026955</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802">
@@ -11594,6 +13999,9 @@
       <c r="E802">
         <v>0.221671613208625</v>
       </c>
+      <c r="F802">
+        <v>0.221671613208625</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803">
@@ -11608,6 +14016,9 @@
       <c r="E803">
         <v>0.3192752883195125</v>
       </c>
+      <c r="F803">
+        <v>0.3192752883195125</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804">
@@ -11622,6 +14033,9 @@
       <c r="E804">
         <v>0.1603521292564484</v>
       </c>
+      <c r="F804">
+        <v>0.1603521292564484</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805">
@@ -11636,6 +14050,9 @@
       <c r="E805">
         <v>0.206082371742687</v>
       </c>
+      <c r="F805">
+        <v>0.206082371742687</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806">
@@ -11650,6 +14067,9 @@
       <c r="E806">
         <v>0.1047822774800945</v>
       </c>
+      <c r="F806">
+        <v>0.1047822774800945</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807">
@@ -11664,6 +14084,9 @@
       <c r="E807">
         <v>1.129670154641031</v>
       </c>
+      <c r="F807">
+        <v>1.129670154641031</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808">
@@ -11678,6 +14101,9 @@
       <c r="E808">
         <v>1.13499025834928</v>
       </c>
+      <c r="F808">
+        <v>1.13499025834928</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809">
@@ -11692,6 +14118,9 @@
       <c r="E809">
         <v>1.198886478119697</v>
       </c>
+      <c r="F809">
+        <v>1.198886478119697</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810">
@@ -11706,6 +14135,9 @@
       <c r="E810">
         <v>1.198715293312789</v>
       </c>
+      <c r="F810">
+        <v>1.198715293312789</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811">
@@ -11720,6 +14152,9 @@
       <c r="E811">
         <v>1.151390005946444</v>
       </c>
+      <c r="F811">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812">
@@ -11734,6 +14169,9 @@
       <c r="E812">
         <v>1.211696273031568</v>
       </c>
+      <c r="F812">
+        <v>1.211696273031568</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813">
@@ -11748,6 +14186,9 @@
       <c r="E813">
         <v>1.169578100120269</v>
       </c>
+      <c r="F813">
+        <v>1.169578100120269</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814">
@@ -11762,6 +14203,9 @@
       <c r="E814">
         <v>1.12181505176422</v>
       </c>
+      <c r="F814">
+        <v>1.12181505176422</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815">
@@ -11776,6 +14220,9 @@
       <c r="E815">
         <v>1.069909613681434</v>
       </c>
+      <c r="F815">
+        <v>1.069909613681434</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816">
@@ -11790,6 +14237,9 @@
       <c r="E816">
         <v>1.017304782266921</v>
       </c>
+      <c r="F816">
+        <v>1.017304782266921</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817">
@@ -11804,6 +14254,9 @@
       <c r="E817">
         <v>0.6621896991631843</v>
       </c>
+      <c r="F817">
+        <v>0.6621896991631843</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818">
@@ -11818,6 +14271,9 @@
       <c r="E818">
         <v>0.5282324926788926</v>
       </c>
+      <c r="F818">
+        <v>0.5282324926788926</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819">
@@ -11832,6 +14288,9 @@
       <c r="E819">
         <v>0.4949900308421299</v>
       </c>
+      <c r="F819">
+        <v>0.4949900308421299</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820">
@@ -11846,6 +14305,9 @@
       <c r="E820">
         <v>0.3799702942179701</v>
       </c>
+      <c r="F820">
+        <v>0.3799702942179701</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821">
@@ -11860,6 +14322,9 @@
       <c r="E821">
         <v>0.3516194437625536</v>
       </c>
+      <c r="F821">
+        <v>0.3516194437625536</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822">
@@ -11874,6 +14339,9 @@
       <c r="E822">
         <v>1.413627087412801</v>
       </c>
+      <c r="F822">
+        <v>1.413627087412801</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823">
@@ -11888,6 +14356,9 @@
       <c r="E823">
         <v>1.342402804450124</v>
       </c>
+      <c r="F823">
+        <v>1.342402804450124</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824">
@@ -11902,6 +14373,9 @@
       <c r="E824">
         <v>1.302529108708484</v>
       </c>
+      <c r="F824">
+        <v>1.302529108708484</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825">
@@ -11916,6 +14390,9 @@
       <c r="E825">
         <v>1.225251140384418</v>
       </c>
+      <c r="F825">
+        <v>1.225251140384418</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826">
@@ -11930,6 +14407,9 @@
       <c r="E826">
         <v>1.151390005946444</v>
       </c>
+      <c r="F826">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827">
@@ -11944,6 +14424,9 @@
       <c r="E827">
         <v>0.117193298827309</v>
       </c>
+      <c r="F827">
+        <v>0.117193298827309</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828">
@@ -11958,6 +14441,9 @@
       <c r="E828">
         <v>0.07142052469243917</v>
       </c>
+      <c r="F828">
+        <v>0.07142052469243917</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829">
@@ -11972,6 +14458,9 @@
       <c r="E829">
         <v>0.05631081608045375</v>
       </c>
+      <c r="F829">
+        <v>0.05631081608045375</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830">
@@ -11986,6 +14475,9 @@
       <c r="E830">
         <v>0.02481510410634525</v>
       </c>
+      <c r="F830">
+        <v>0.02481510410634525</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831">
@@ -12000,6 +14492,9 @@
       <c r="E831">
         <v>0.01325114640373815</v>
       </c>
+      <c r="F831">
+        <v>0.01325114640373815</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832">
@@ -12014,6 +14509,9 @@
       <c r="E832">
         <v>0.2597735975234544</v>
       </c>
+      <c r="F832">
+        <v>0.2597735975234544</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833">
@@ -12028,6 +14526,9 @@
       <c r="E833">
         <v>0.2709076715889983</v>
       </c>
+      <c r="F833">
+        <v>0.2709076715889983</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834">
@@ -12042,6 +14543,9 @@
       <c r="E834">
         <v>0.2860718700567156</v>
       </c>
+      <c r="F834">
+        <v>0.2860718700567156</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835">
@@ -12056,6 +14560,9 @@
       <c r="E835">
         <v>0.2909157576905614</v>
       </c>
+      <c r="F835">
+        <v>0.2909157576905614</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836">
@@ -12070,6 +14577,9 @@
       <c r="E836">
         <v>0.3014603241936731</v>
       </c>
+      <c r="F836">
+        <v>0.3014603241936731</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837">
@@ -12084,6 +14594,9 @@
       <c r="E837">
         <v>0.9749584898237784</v>
       </c>
+      <c r="F837">
+        <v>0.9749584898237784</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838">
@@ -12098,6 +14611,9 @@
       <c r="E838">
         <v>0.8894791555205397</v>
       </c>
+      <c r="F838">
+        <v>0.8894791555205397</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839">
@@ -12112,6 +14628,9 @@
       <c r="E839">
         <v>0.8121873232932756</v>
       </c>
+      <c r="F839">
+        <v>0.8121873232932756</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840">
@@ -12126,6 +14645,9 @@
       <c r="E840">
         <v>0.7314095216564088</v>
       </c>
+      <c r="F840">
+        <v>0.7314095216564088</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841">
@@ -12140,6 +14662,9 @@
       <c r="E841">
         <v>0.6609858843340065</v>
       </c>
+      <c r="F841">
+        <v>0.6609858843340065</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842">
@@ -12154,6 +14679,9 @@
       <c r="E842">
         <v>0.578171688815979</v>
       </c>
+      <c r="F842">
+        <v>0.578171688815979</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843">
@@ -12168,6 +14696,9 @@
       <c r="E843">
         <v>0.5696478588728568</v>
       </c>
+      <c r="F843">
+        <v>0.5696478588728568</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844">
@@ -12182,6 +14713,9 @@
       <c r="E844">
         <v>0.5999809160248437</v>
       </c>
+      <c r="F844">
+        <v>0.5999809160248437</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845">
@@ -12196,6 +14730,9 @@
       <c r="E845">
         <v>0.6047131029149679</v>
       </c>
+      <c r="F845">
+        <v>0.6047131029149679</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846">
@@ -12210,6 +14747,9 @@
       <c r="E846">
         <v>0.6146743969033225</v>
       </c>
+      <c r="F846">
+        <v>0.6146743969033225</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847">
@@ -12224,6 +14764,9 @@
       <c r="E847">
         <v>-2.51205226878745</v>
       </c>
+      <c r="F847">
+        <v>-2.51205226878745</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848">
@@ -12238,6 +14781,9 @@
       <c r="E848">
         <v>-2.709936719770926</v>
       </c>
+      <c r="F848">
+        <v>-2.709936719770926</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849">
@@ -12252,6 +14798,9 @@
       <c r="E849">
         <v>-2.774580567479985</v>
       </c>
+      <c r="F849">
+        <v>-2.774580567479985</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850">
@@ -12266,6 +14815,9 @@
       <c r="E850">
         <v>-2.871454694137453</v>
       </c>
+      <c r="F850">
+        <v>-2.871454694137453</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851">
@@ -12280,6 +14832,9 @@
       <c r="E851">
         <v>-2.877010105564159</v>
       </c>
+      <c r="F851">
+        <v>-2.877010105564159</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852">
@@ -12294,6 +14849,9 @@
       <c r="E852">
         <v>-1.640485690217405</v>
       </c>
+      <c r="F852">
+        <v>-1.640485690217405</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853">
@@ -12308,6 +14866,9 @@
       <c r="E853">
         <v>-1.184987415484642</v>
       </c>
+      <c r="F853">
+        <v>-1.184987415484642</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854">
@@ -12322,6 +14883,9 @@
       <c r="E854">
         <v>-0.9809071390723733</v>
       </c>
+      <c r="F854">
+        <v>-0.9809071390723733</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855">
@@ -12336,6 +14900,9 @@
       <c r="E855">
         <v>-0.7064547216591694</v>
       </c>
+      <c r="F855">
+        <v>-0.7064547216591694</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856">
@@ -12350,6 +14917,9 @@
       <c r="E856">
         <v>-0.4841555170842334</v>
       </c>
+      <c r="F856">
+        <v>-0.4841555170842334</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857">
@@ -12364,6 +14934,9 @@
       <c r="E857">
         <v>0.0892712139016922</v>
       </c>
+      <c r="F857">
+        <v>0.0892712139016922</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858">
@@ -12378,6 +14951,9 @@
       <c r="E858">
         <v>0.03970680035215682</v>
       </c>
+      <c r="F858">
+        <v>0.03970680035215682</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859">
@@ -12392,6 +14968,9 @@
       <c r="E859">
         <v>0.02910152677443326</v>
       </c>
+      <c r="F859">
+        <v>0.02910152677443326</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860">
@@ -12406,6 +14985,9 @@
       <c r="E860">
         <v>0.00246962334897747</v>
       </c>
+      <c r="F860">
+        <v>0.00246962334897747</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861">
@@ -12420,6 +15002,9 @@
       <c r="E861">
         <v>-0.004206281729981559</v>
       </c>
+      <c r="F861">
+        <v>-0.004206281729981559</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862">
@@ -12434,6 +15019,9 @@
       <c r="E862">
         <v>1.081274394929276</v>
       </c>
+      <c r="F862">
+        <v>1.081274394929276</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863">
@@ -12448,6 +15036,9 @@
       <c r="E863">
         <v>1.022716893047432</v>
       </c>
+      <c r="F863">
+        <v>1.022716893047432</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864">
@@ -12462,6 +15053,9 @@
       <c r="E864">
         <v>0.9646180268270578</v>
       </c>
+      <c r="F864">
+        <v>0.9646180268270578</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865">
@@ -12476,6 +15070,9 @@
       <c r="E865">
         <v>0.9019652955817947</v>
       </c>
+      <c r="F865">
+        <v>0.9019652955817947</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866">
@@ -12490,6 +15087,9 @@
       <c r="E866">
         <v>0.8437400500336818</v>
       </c>
+      <c r="F866">
+        <v>0.8437400500336818</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867">
@@ -12504,6 +15104,9 @@
       <c r="E867">
         <v>0.3249531040112667</v>
       </c>
+      <c r="F867">
+        <v>0.3249531040112667</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868">
@@ -12518,6 +15121,9 @@
       <c r="E868">
         <v>0.3322108412201586</v>
       </c>
+      <c r="F868">
+        <v>0.3322108412201586</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869">
@@ -12532,6 +15138,9 @@
       <c r="E869">
         <v>0.2687710266943658</v>
       </c>
+      <c r="F869">
+        <v>0.2687710266943658</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870">
@@ -12546,6 +15155,9 @@
       <c r="E870">
         <v>0.2242598542765452</v>
       </c>
+      <c r="F870">
+        <v>0.2242598542765452</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871">
@@ -12560,6 +15172,9 @@
       <c r="E871">
         <v>0.1880026552318367</v>
       </c>
+      <c r="F871">
+        <v>0.1880026552318367</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872">
@@ -12574,6 +15189,9 @@
       <c r="E872">
         <v>-0.4056337269277645</v>
       </c>
+      <c r="F872">
+        <v>-0.4056337269277645</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873">
@@ -12588,6 +15206,9 @@
       <c r="E873">
         <v>-0.5479642791063452</v>
       </c>
+      <c r="F873">
+        <v>-0.5479642791063452</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874">
@@ -12602,6 +15223,9 @@
       <c r="E874">
         <v>-0.6014290516267795</v>
       </c>
+      <c r="F874">
+        <v>-0.6014290516267795</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875">
@@ -12616,6 +15240,9 @@
       <c r="E875">
         <v>-0.6798011791670011</v>
       </c>
+      <c r="F875">
+        <v>-0.6798011791670011</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876">
@@ -12630,6 +15257,9 @@
       <c r="E876">
         <v>-0.7150612206621606</v>
       </c>
+      <c r="F876">
+        <v>-0.7150612206621606</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877">
@@ -12644,6 +15274,9 @@
       <c r="E877">
         <v>-0.68313477205731</v>
       </c>
+      <c r="F877">
+        <v>-0.68313477205731</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878">
@@ -12658,6 +15291,9 @@
       <c r="E878">
         <v>-0.7679042452117449</v>
       </c>
+      <c r="F878">
+        <v>-0.7679042452117449</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879">
@@ -12672,6 +15308,9 @@
       <c r="E879">
         <v>-0.7919613206273464</v>
       </c>
+      <c r="F879">
+        <v>-0.7919613206273464</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880">
@@ -12686,6 +15325,9 @@
       <c r="E880">
         <v>-0.8377708017398784</v>
       </c>
+      <c r="F880">
+        <v>-0.8377708017398784</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881">
@@ -12700,6 +15342,9 @@
       <c r="E881">
         <v>-0.8430202168263182</v>
       </c>
+      <c r="F881">
+        <v>-0.8430202168263182</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882">
@@ -12714,6 +15359,9 @@
       <c r="E882">
         <v>0.2551924801958286</v>
       </c>
+      <c r="F882">
+        <v>0.2551924801958286</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883">
@@ -12728,6 +15376,9 @@
       <c r="E883">
         <v>0.1672863082676845</v>
       </c>
+      <c r="F883">
+        <v>0.1672863082676845</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884">
@@ -12742,6 +15393,9 @@
       <c r="E884">
         <v>0.1107876612603156</v>
       </c>
+      <c r="F884">
+        <v>0.1107876612603156</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885">
@@ -12756,6 +15410,9 @@
       <c r="E885">
         <v>0.04309610781218869</v>
       </c>
+      <c r="F885">
+        <v>0.04309610781218869</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886">
@@ -12770,6 +15427,9 @@
       <c r="E886">
         <v>-0.0007201963884752875</v>
       </c>
+      <c r="F886">
+        <v>-0.0007201963884752875</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887">
@@ -12784,6 +15444,9 @@
       <c r="E887">
         <v>1.120837870274889</v>
       </c>
+      <c r="F887">
+        <v>1.120837870274889</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888">
@@ -12798,6 +15461,9 @@
       <c r="E888">
         <v>1.127931436267741</v>
       </c>
+      <c r="F888">
+        <v>1.127931436267741</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889">
@@ -12812,6 +15478,9 @@
       <c r="E889">
         <v>1.139152477091258</v>
       </c>
+      <c r="F889">
+        <v>1.139152477091258</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890">
@@ -12826,6 +15495,9 @@
       <c r="E890">
         <v>1.136094674292207</v>
       </c>
+      <c r="F890">
+        <v>1.136094674292207</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891">
@@ -12840,6 +15512,9 @@
       <c r="E891">
         <v>1.125970060661805</v>
       </c>
+      <c r="F891">
+        <v>1.125970060661805</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892">
@@ -12854,6 +15529,9 @@
       <c r="E892">
         <v>-1.003330219472194</v>
       </c>
+      <c r="F892">
+        <v>-1.003330219472194</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893">
@@ -12868,6 +15546,9 @@
       <c r="E893">
         <v>-1.168584540043674</v>
       </c>
+      <c r="F893">
+        <v>-1.168584540043674</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894">
@@ -12882,6 +15563,9 @@
       <c r="E894">
         <v>-1.252615222345689</v>
       </c>
+      <c r="F894">
+        <v>-1.252615222345689</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895">
@@ -12896,6 +15580,9 @@
       <c r="E895">
         <v>-1.355075028853722</v>
       </c>
+      <c r="F895">
+        <v>-1.355075028853722</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896">
@@ -12910,6 +15597,9 @@
       <c r="E896">
         <v>-1.398801149932358</v>
       </c>
+      <c r="F896">
+        <v>-1.398801149932358</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897">
@@ -12924,6 +15614,9 @@
       <c r="E897">
         <v>0.9298704305934119</v>
       </c>
+      <c r="F897">
+        <v>0.9298704305934119</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898">
@@ -12938,6 +15631,9 @@
       <c r="E898">
         <v>0.9082759056963183</v>
       </c>
+      <c r="F898">
+        <v>0.9082759056963183</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899">
@@ -12952,6 +15648,9 @@
       <c r="E899">
         <v>0.8895462474756256</v>
       </c>
+      <c r="F899">
+        <v>0.8895462474756256</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900">
@@ -12966,6 +15665,9 @@
       <c r="E900">
         <v>0.8610361656938609</v>
       </c>
+      <c r="F900">
+        <v>0.8610361656938609</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901">
@@ -12980,6 +15682,9 @@
       <c r="E901">
         <v>0.8337754711029233</v>
       </c>
+      <c r="F901">
+        <v>0.8337754711029233</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902">
@@ -12994,6 +15699,9 @@
       <c r="E902">
         <v>0.6959707004550673</v>
       </c>
+      <c r="F902">
+        <v>0.6959707004550673</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903">
@@ -13008,6 +15716,9 @@
       <c r="E903">
         <v>0.623022612725551</v>
       </c>
+      <c r="F903">
+        <v>0.623022612725551</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904">
@@ -13022,6 +15733,9 @@
       <c r="E904">
         <v>0.5319773748606402</v>
       </c>
+      <c r="F904">
+        <v>0.5319773748606402</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905">
@@ -13036,6 +15750,9 @@
       <c r="E905">
         <v>0.4625181165910137</v>
       </c>
+      <c r="F905">
+        <v>0.4625181165910137</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906">
@@ -13050,6 +15767,9 @@
       <c r="E906">
         <v>0.3887146561045031</v>
       </c>
+      <c r="F906">
+        <v>0.3887146561045031</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907">
@@ -13064,6 +15784,9 @@
       <c r="E907">
         <v>0.7064420423260748</v>
       </c>
+      <c r="F907">
+        <v>0.7064420423260748</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908">
@@ -13078,6 +15801,9 @@
       <c r="E908">
         <v>0.6194584788761694</v>
       </c>
+      <c r="F908">
+        <v>0.6194584788761694</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909">
@@ -13092,6 +15818,9 @@
       <c r="E909">
         <v>0.5519421731040475</v>
       </c>
+      <c r="F909">
+        <v>0.5519421731040475</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910">
@@ -13106,6 +15835,9 @@
       <c r="E910">
         <v>0.4773106490619924</v>
       </c>
+      <c r="F910">
+        <v>0.4773106490619924</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911">
@@ -13120,6 +15852,9 @@
       <c r="E911">
         <v>0.4179761475749978</v>
       </c>
+      <c r="F911">
+        <v>0.4179761475749978</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912">
@@ -13134,6 +15869,9 @@
       <c r="E912">
         <v>-0.1032052447192334</v>
       </c>
+      <c r="F912">
+        <v>-0.1032052447192334</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913">
@@ -13148,6 +15886,9 @@
       <c r="E913">
         <v>-0.2450386327989577</v>
       </c>
+      <c r="F913">
+        <v>-0.2450386327989577</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914">
@@ -13162,6 +15903,9 @@
       <c r="E914">
         <v>-0.3374588428624899</v>
       </c>
+      <c r="F914">
+        <v>-0.3374588428624899</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915">
@@ -13176,6 +15920,9 @@
       <c r="E915">
         <v>-0.4403258905917493</v>
       </c>
+      <c r="F915">
+        <v>-0.4403258905917493</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916">
@@ -13190,6 +15937,9 @@
       <c r="E916">
         <v>-0.5045027168835755</v>
       </c>
+      <c r="F916">
+        <v>-0.5045027168835755</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917">
@@ -13204,6 +15954,9 @@
       <c r="E917">
         <v>-0.1421851202603109</v>
       </c>
+      <c r="F917">
+        <v>-0.1421851202603109</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918">
@@ -13218,6 +15971,9 @@
       <c r="E918">
         <v>-0.3457129835245125</v>
       </c>
+      <c r="F918">
+        <v>-0.3457129835245125</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919">
@@ -13232,6 +15988,9 @@
       <c r="E919">
         <v>-0.4886379393634002</v>
       </c>
+      <c r="F919">
+        <v>-0.4886379393634002</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920">
@@ -13246,6 +16005,9 @@
       <c r="E920">
         <v>-0.6372639518251496</v>
       </c>
+      <c r="F920">
+        <v>-0.6372639518251496</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921">
@@ -13260,6 +16022,9 @@
       <c r="E921">
         <v>-0.7373148412835678</v>
       </c>
+      <c r="F921">
+        <v>-0.7373148412835678</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922">
@@ -13274,6 +16039,9 @@
       <c r="E922">
         <v>-0.2916641198771784</v>
       </c>
+      <c r="F922">
+        <v>-0.2916641198771784</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923">
@@ -13288,6 +16056,9 @@
       <c r="E923">
         <v>-0.3085052536002543</v>
       </c>
+      <c r="F923">
+        <v>-0.3085052536002543</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924">
@@ -13302,6 +16073,9 @@
       <c r="E924">
         <v>-0.285709282758382</v>
       </c>
+      <c r="F924">
+        <v>-0.285709282758382</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925">
@@ -13316,6 +16090,9 @@
       <c r="E925">
         <v>-0.2861392632922249</v>
       </c>
+      <c r="F925">
+        <v>-0.2861392632922249</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926">
@@ -13330,6 +16107,9 @@
       <c r="E926">
         <v>-0.2635751510925007</v>
       </c>
+      <c r="F926">
+        <v>-0.2635751510925007</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927">
@@ -13344,6 +16124,9 @@
       <c r="E927">
         <v>0.9438907755136324</v>
       </c>
+      <c r="F927">
+        <v>0.9438907755136324</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928">
@@ -13358,6 +16141,9 @@
       <c r="E928">
         <v>0.997240839529104</v>
       </c>
+      <c r="F928">
+        <v>0.997240839529104</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929">
@@ -13372,6 +16158,9 @@
       <c r="E929">
         <v>1.047290508986125</v>
       </c>
+      <c r="F929">
+        <v>1.047290508986125</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930">
@@ -13386,6 +16175,9 @@
       <c r="E930">
         <v>1.082807023785859</v>
       </c>
+      <c r="F930">
+        <v>1.082807023785859</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931">
@@ -13400,6 +16192,9 @@
       <c r="E931">
         <v>1.107458297080212</v>
       </c>
+      <c r="F931">
+        <v>1.107458297080212</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932">
@@ -13414,6 +16209,9 @@
       <c r="E932">
         <v>1.201815411242342</v>
       </c>
+      <c r="F932">
+        <v>1.201815411242342</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933">
@@ -13428,6 +16226,9 @@
       <c r="E933">
         <v>1.172838770471766</v>
       </c>
+      <c r="F933">
+        <v>1.172838770471766</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934">
@@ -13442,6 +16243,9 @@
       <c r="E934">
         <v>1.137212660186094</v>
       </c>
+      <c r="F934">
+        <v>1.137212660186094</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935">
@@ -13456,6 +16260,9 @@
       <c r="E935">
         <v>1.095855406666697</v>
       </c>
+      <c r="F935">
+        <v>1.095855406666697</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936">
@@ -13470,6 +16277,9 @@
       <c r="E936">
         <v>1.052109143740525</v>
       </c>
+      <c r="F936">
+        <v>1.052109143740525</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937">
@@ -13484,6 +16294,9 @@
       <c r="E937">
         <v>1.125109910217472</v>
       </c>
+      <c r="F937">
+        <v>1.125109910217472</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938">
@@ -13498,6 +16311,9 @@
       <c r="E938">
         <v>1.025514634212245</v>
       </c>
+      <c r="F938">
+        <v>1.025514634212245</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939">
@@ -13512,6 +16328,9 @@
       <c r="E939">
         <v>0.9305430609444079</v>
       </c>
+      <c r="F939">
+        <v>0.9305430609444079</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940">
@@ -13526,6 +16345,9 @@
       <c r="E940">
         <v>0.8347186367670291</v>
       </c>
+      <c r="F940">
+        <v>0.8347186367670291</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941">
@@ -13540,6 +16362,9 @@
       <c r="E941">
         <v>0.7486701848687038</v>
       </c>
+      <c r="F941">
+        <v>0.7486701848687038</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942">
@@ -13554,6 +16379,9 @@
       <c r="E942">
         <v>1.565628013236011</v>
       </c>
+      <c r="F942">
+        <v>1.565628013236011</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943">
@@ -13568,6 +16396,9 @@
       <c r="E943">
         <v>1.466113515427544</v>
       </c>
+      <c r="F943">
+        <v>1.466113515427544</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944">
@@ -13582,6 +16413,9 @@
       <c r="E944">
         <v>1.357843957484835</v>
       </c>
+      <c r="F944">
+        <v>1.357843957484835</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945">
@@ -13596,6 +16430,9 @@
       <c r="E945">
         <v>1.253765097406694</v>
       </c>
+      <c r="F945">
+        <v>1.253765097406694</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946">
@@ -13610,6 +16447,9 @@
       <c r="E946">
         <v>1.151390005946444</v>
       </c>
+      <c r="F946">
+        <v>1.151390005946444</v>
+      </c>
     </row>
     <row r="947">
       <c r="A947">
@@ -13664,6 +16504,9 @@
       <c r="E952">
         <v>-0.8862223474191362</v>
       </c>
+      <c r="F952">
+        <v>-0.8862223474191362</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953">
@@ -13678,6 +16521,9 @@
       <c r="E953">
         <v>-0.722509377990101</v>
       </c>
+      <c r="F953">
+        <v>-0.722509377990101</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954">
@@ -13692,6 +16538,9 @@
       <c r="E954">
         <v>-0.5296057751977333</v>
       </c>
+      <c r="F954">
+        <v>-0.5296057751977333</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955">
@@ -13706,6 +16555,9 @@
       <c r="E955">
         <v>-0.3829056185777875</v>
       </c>
+      <c r="F955">
+        <v>-0.3829056185777875</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956">
@@ -13720,6 +16572,9 @@
       <c r="E956">
         <v>-0.229320567102531</v>
       </c>
+      <c r="F956">
+        <v>-0.229320567102531</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957">
@@ -13734,6 +16589,9 @@
       <c r="E957">
         <v>0.3520894511204608</v>
       </c>
+      <c r="F957">
+        <v>0.3520894511204608</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958">
@@ -13748,6 +16606,9 @@
       <c r="E958">
         <v>0.2379951019788906</v>
       </c>
+      <c r="F958">
+        <v>0.2379951019788906</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959">
@@ -13762,6 +16623,9 @@
       <c r="E959">
         <v>0.1877988789214066</v>
       </c>
+      <c r="F959">
+        <v>0.1877988789214066</v>
+      </c>
     </row>
     <row r="960">
       <c r="A960">
@@ -13776,6 +16640,9 @@
       <c r="E960">
         <v>0.09984296644030574</v>
       </c>
+      <c r="F960">
+        <v>0.09984296644030574</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961">
@@ -13790,6 +16657,9 @@
       <c r="E961">
         <v>0.05819649077799506</v>
       </c>
+      <c r="F961">
+        <v>0.05819649077799506</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962">
@@ -13804,6 +16674,9 @@
       <c r="E962">
         <v>-0.2390649518368533</v>
       </c>
+      <c r="F962">
+        <v>-0.2390649518368533</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963">
@@ -13818,6 +16691,9 @@
       <c r="E963">
         <v>-0.07402280016551702</v>
       </c>
+      <c r="F963">
+        <v>-0.07402280016551702</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964">
@@ -13832,6 +16708,9 @@
       <c r="E964">
         <v>0.09752116334666659</v>
       </c>
+      <c r="F964">
+        <v>0.09752116334666659</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965">
@@ -13846,6 +16725,9 @@
       <c r="E965">
         <v>0.2305796574520491</v>
       </c>
+      <c r="F965">
+        <v>0.2305796574520491</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966">
@@ -13860,6 +16742,9 @@
       <c r="E966">
         <v>0.3590241899113793</v>
       </c>
+      <c r="F966">
+        <v>0.3590241899113793</v>
+      </c>
     </row>
     <row r="967">
       <c r="A967">
@@ -13874,6 +16759,9 @@
       <c r="E967">
         <v>-2.029759997557345</v>
       </c>
+      <c r="F967">
+        <v>-2.029759997557345</v>
+      </c>
     </row>
     <row r="968">
       <c r="A968">
@@ -13888,6 +16776,9 @@
       <c r="E968">
         <v>-2.344515583149392</v>
       </c>
+      <c r="F968">
+        <v>-2.344515583149392</v>
+      </c>
     </row>
     <row r="969">
       <c r="A969">
@@ -13902,6 +16793,9 @@
       <c r="E969">
         <v>-2.513468047209688</v>
       </c>
+      <c r="F969">
+        <v>-2.513468047209688</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970">
@@ -13916,6 +16810,9 @@
       <c r="E970">
         <v>-2.710606587220455</v>
       </c>
+      <c r="F970">
+        <v>-2.710606587220455</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971">
@@ -13930,6 +16827,9 @@
       <c r="E971">
         <v>-2.800581284704568</v>
       </c>
+      <c r="F971">
+        <v>-2.800581284704568</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972">
@@ -13944,6 +16844,9 @@
       <c r="E972">
         <v>0.4210270779406395</v>
       </c>
+      <c r="F972">
+        <v>0.4210270779406395</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973">
@@ -13958,6 +16861,9 @@
       <c r="E973">
         <v>0.2055432264207067</v>
       </c>
+      <c r="F973">
+        <v>0.2055432264207067</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974">
@@ -13972,6 +16878,9 @@
       <c r="E974">
         <v>0.3766552036033351</v>
       </c>
+      <c r="F974">
+        <v>0.3766552036033351</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975">
@@ -13986,6 +16895,9 @@
       <c r="E975">
         <v>0.3052395962657742</v>
       </c>
+      <c r="F975">
+        <v>0.3052395962657742</v>
+      </c>
     </row>
     <row r="976">
       <c r="A976">
@@ -14000,6 +16912,9 @@
       <c r="E976">
         <v>0.3750774779929322</v>
       </c>
+      <c r="F976">
+        <v>0.3750774779929322</v>
+      </c>
     </row>
     <row r="977">
       <c r="A977">
@@ -14014,6 +16929,9 @@
       <c r="E977">
         <v>-0.3160956452063676</v>
       </c>
+      <c r="F977">
+        <v>-0.3160956452063676</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978">
@@ -14028,6 +16946,9 @@
       <c r="E978">
         <v>-0.2569697597142119</v>
       </c>
+      <c r="F978">
+        <v>-0.2569697597142119</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979">
@@ -14042,6 +16963,9 @@
       <c r="E979">
         <v>-0.1666545150736775</v>
       </c>
+      <c r="F979">
+        <v>-0.1666545150736775</v>
+      </c>
     </row>
     <row r="980">
       <c r="A980">
@@ -14056,6 +16980,9 @@
       <c r="E980">
         <v>-0.1064005663196673</v>
       </c>
+      <c r="F980">
+        <v>-0.1064005663196673</v>
+      </c>
     </row>
     <row r="981">
       <c r="A981">
@@ -14070,6 +16997,9 @@
       <c r="E981">
         <v>-0.03439746253448384</v>
       </c>
+      <c r="F981">
+        <v>-0.03439746253448384</v>
+      </c>
     </row>
     <row r="982">
       <c r="A982">
@@ -14084,6 +17014,9 @@
       <c r="E982">
         <v>-2.293333924007598</v>
       </c>
+      <c r="F982">
+        <v>-2.293333924007598</v>
+      </c>
     </row>
     <row r="983">
       <c r="A983">
@@ -14098,6 +17031,9 @@
       <c r="E983">
         <v>-2.745056102781502</v>
       </c>
+      <c r="F983">
+        <v>-2.745056102781502</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984">
@@ -14112,6 +17048,9 @@
       <c r="E984">
         <v>-3.0379782191282</v>
       </c>
+      <c r="F984">
+        <v>-3.0379782191282</v>
+      </c>
     </row>
     <row r="985">
       <c r="A985">
@@ -14126,6 +17065,9 @@
       <c r="E985">
         <v>-3.339185198695242</v>
       </c>
+      <c r="F985">
+        <v>-3.339185198695242</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986">
@@ -14138,6 +17080,9 @@
         <v>48.88173394700215</v>
       </c>
       <c r="E986">
+        <v>-3.514200357329863</v>
+      </c>
+      <c r="F986">
         <v>-3.514200357329863</v>
       </c>
     </row>
